--- a/📁 TrickPilot/📊 TrickPilot_Websites_Master_List.xlsx
+++ b/📁 TrickPilot/📊 TrickPilot_Websites_Master_List.xlsx
@@ -470,14 +470,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F231"/>
+  <dimension ref="A1:F230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -494,17 +494,17 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Official Website URL</t>
+          <t>Exact Official Website URL</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Key Function / Description</t>
+          <t>Key Function / Purpose (TrickPilot)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Source Video Title</t>
+          <t>Source Video Title (TrickPilot)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -521,27 +521,27 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>GPTExcel</t>
+          <t>1000s of png images</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>https://gptexcel.io</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>AI generator for Microsoft Excel &amp; Google Sheets formulas, scripts, and SQL queries.</t>
+          <t>Online productivity web tool featured in TrickPilot: Get 1000s of PNG Images</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Excel Tips</t>
+          <t>Get 1000s of PNG Images</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/zGBMGORdpyA</t>
+          <t>https://www.youtube.com/shorts/qynUBztz37g</t>
         </is>
       </c>
     </row>
@@ -553,6843 +553,6843 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>TypeRacer / Keybr</t>
+          <t>1gb data free anytime</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>https://play.typeracer.com</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Multiplayer typing speed test and keyboard touch-typing practice web app.</t>
+          <t>Online productivity web tool featured in TrickPilot: Get 1GB Data Free Anytime</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>Wishlist this typing game</t>
+          <t>Get 1GB Data Free Anytime</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/m6LBfv7E1BU</t>
+          <t>https://www.youtube.com/shorts/cKHTayk0sUI</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>🎨 Design, 3D &amp; Graphics</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Its just launched and its so perfect</t>
+          <t>3 useful websites</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Its+just+launched+and+its+so+perfect</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Its just launched and its so perfect</t>
+          <t>Online productivity web tool featured in TrickPilot: 3 Useful Websites</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Its just launched and its so perfect</t>
+          <t>3 Useful Websites</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/wjkgZ1GsvRw</t>
+          <t>https://www.youtube.com/shorts/tB1syoclfqw</t>
         </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>🎮 Gaming &amp; Fun Web Experiments</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Games to play in Browser</t>
+          <t>3 websites to cure boredom</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Games+to+play+in+Browser</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Games to play in Browser</t>
+          <t>Online productivity web tool featured in TrickPilot: 3 Websites to Cure Boredom</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Games to play in Browser</t>
+          <t>3 Websites to Cure Boredom</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/Cs6Ha8bA0WE</t>
+          <t>https://www.youtube.com/shorts/rFWwLY84SJw</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>🎮 Gaming &amp; Fun Web Experiments</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Try These Website When You Feel Bored</t>
+          <t>99% freelancers dont know</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Try+These+Website+When+You+Feel+Bored</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Try These Website When You Feel Bored</t>
+          <t>Online productivity web tool featured in TrickPilot: 99% Freelancers dont know</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Try These Website When You Feel Bored</t>
+          <t>99% Freelancers dont know</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/S_PHAjDHKHY</t>
+          <t>https://www.youtube.com/shorts/NqksSbUpBZQ</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>🎮 Gaming &amp; Fun Web Experiments</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Watch this before buying laptop</t>
+          <t>A buisness plan in seconds</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Watch+this+before+buying+laptop</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Watch this before buying laptop</t>
+          <t>Online productivity web tool featured in TrickPilot: Get a buisness plan in seconds</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Watch this before buying laptop</t>
+          <t>Get a buisness plan in seconds</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/-zLSi0RVCrU</t>
+          <t>https://www.youtube.com/shorts/H_A3k_d7txs</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>💻 Coding &amp; Web Development</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Create Website In Just 5 Minutes</t>
+          <t>Access your pc from anywhere</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Create+Website+In+Just+5+Minutes</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Create Website In Just 5 Minutes</t>
+          <t>Online productivity web tool featured in TrickPilot: Access Your PC From Anywhere</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Create Website In Just 5 Minutes</t>
+          <t>Access Your PC From Anywhere</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/-6CjzhPtJ24</t>
+          <t>https://www.youtube.com/shorts/Mw1TTO7YeNw</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>💻 Coding &amp; Web Development</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Make 3D Website In Just 5 Min For Your Busine</t>
+          <t>Add text behind image</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Make+3D+Website+In+Just+5+Min+For+Your+Business</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Make 3D Website In Just 5 Min For Your Business</t>
+          <t>Online productivity web tool featured in TrickPilot: Add Text Behind Image</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Make 3D Website In Just 5 Min For Your Business</t>
+          <t>Add Text Behind Image</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/wDPBfOqTayk</t>
+          <t>https://www.youtube.com/shorts/0E78zioOxkg</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>3 Most Useful Websites For Students</t>
+          <t>Ai is becoming so dangerous</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=3+Most+Useful+Websites+For+Students</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: 3 Most Useful Websites For Students</t>
+          <t>Online productivity web tool featured in TrickPilot: Ai is becoming so dangerous</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3 Most Useful Websites For Students</t>
+          <t>Ai is becoming so dangerous</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/t_CIeNfo4JI</t>
+          <t>https://www.youtube.com/shorts/UKyB7Hb_WWE</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>3 Useful Websites</t>
+          <t>All ai tools free for indians? bro,</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=3+Useful+Websites</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: 3 Useful Websites</t>
+          <t>Online productivity web tool featured in TrickPilot: All AI tools free for Indians? Bro, were part of an experiment</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>3 Useful Websites</t>
+          <t>All AI tools free for Indians? Bro, were part of an experiment</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/tB1syoclfqw</t>
+          <t>https://www.youtube.com/shorts/3VV57-IE7a0</t>
         </is>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>3 Websites to Cure Boredom</t>
+          <t>All good</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=3+Websites+to+Cure+Boredom</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: 3 Websites to Cure Boredom</t>
+          <t>Online productivity web tool featured in TrickPilot: All good</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3 Websites to Cure Boredom</t>
+          <t>All good</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/rFWwLY84SJw</t>
+          <t>https://www.youtube.com/shorts/Ar2rH921HM4</t>
         </is>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>60 Ai Agents working on one project at the sa</t>
+          <t>All image tools at one place</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=60+Ai+Agents+working+on+one+project+at+the+same+time</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: 60 Ai Agents working on one project at the same time</t>
+          <t>Online productivity web tool featured in TrickPilot: All Image Tools at one place</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>60 Ai Agents working on one project at the same time</t>
+          <t>All Image Tools at one place</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/KqpjMg8mBmc</t>
+          <t>https://www.youtube.com/shorts/eNA9qBp9LcU</t>
         </is>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>99% Freelancers dont know</t>
+          <t>Are you single</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=99+Freelancers+dont+know</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: 99% Freelancers dont know</t>
+          <t>Online productivity web tool featured in TrickPilot: Are you Single</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>99% Freelancers dont know</t>
+          <t>Are you Single</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/NqksSbUpBZQ</t>
+          <t>Watch This  #shorts #pc</t>
         </is>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Access Your PC From Anywhere</t>
+          <t>Boost your pc performance</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Access+Your+PC+From+Anywhere</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Access Your PC From Anywhere</t>
+          <t>Online productivity web tool featured in TrickPilot: Boost your PC Performance</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Access Your PC From Anywhere</t>
+          <t>Boost your PC Performance</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/Mw1TTO7YeNw</t>
+          <t>https://www.youtube.com/shorts/k2G63P0XQTU</t>
         </is>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Add Text Behind Image</t>
+          <t>Business tips boost your business</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Add+Text+Behind+Image</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Add Text Behind Image</t>
+          <t>Online productivity web tool featured in TrickPilot: business tips boost your business</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Add Text Behind Image</t>
+          <t>business tips boost your business</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/0E78zioOxkg</t>
+          <t>https://www.youtube.com/shorts/Gp_jlrwz-HI</t>
         </is>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Ai is becoming so dangerous</t>
+          <t>Business website in 4 steps</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Ai+is+becoming+so+dangerous</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Ai is becoming so dangerous</t>
+          <t>Online productivity web tool featured in TrickPilot: Create Business Website in 4 Steps</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Ai is becoming so dangerous</t>
+          <t>Create Business Website in 4 Steps</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/UKyB7Hb_WWE</t>
+          <t>https://www.youtube.com/shorts/aPxjgiLsMfc</t>
         </is>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>All AI tools free for Indians? Bro, were part</t>
+          <t>Chinas new image - gen model</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=All+AI+tools+free+for+Indians+Bro+were+part+of+an+experiment</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: All AI tools free for Indians? Bro, were part of an experiment</t>
+          <t>Online productivity web tool featured in TrickPilot: Chinas New Image - Gen Model</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>All AI tools free for Indians? Bro, were part of an experiment</t>
+          <t>Chinas New Image - Gen Model</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/3VV57-IE7a0</t>
+          <t>https://www.youtube.com/shorts/x6H0AZF6eq8</t>
         </is>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>All Image Tools at one place</t>
+          <t>Claim your free 1 year perplexity pro</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=All+Image+Tools+at+one+place</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: All Image Tools at one place</t>
+          <t>Online productivity web tool featured in TrickPilot: Claim your Free 1 Year Perplexity Pro</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>All Image Tools at one place</t>
+          <t>Claim your Free 1 Year Perplexity Pro</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/eNA9qBp9LcU</t>
+          <t>https://www.youtube.com/shorts/6QPWCd41HcI</t>
         </is>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>All good</t>
+          <t>Computer prank to play on your friends</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=All+good</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: All good</t>
+          <t>Online productivity web tool featured in TrickPilot: Computer Prank To Play On Your Friends</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>All good</t>
+          <t>Computer Prank To Play On Your Friends</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/Ar2rH921HM4</t>
+          <t>https://www.youtube.com/shorts/fgzyb0WzLFg</t>
         </is>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Are you Single</t>
+          <t>Convert ai to human</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Are+you+Single</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Are you Single</t>
+          <t>Online productivity web tool featured in TrickPilot: Convert AI to Human</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Are you Single</t>
+          <t>Convert AI to Human</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>Watch This  #shorts #pc</t>
+          <t>https://www.youtube.com/shorts/y27EvICFffM</t>
         </is>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Audio overview is my personal favourite</t>
+          <t>Convert normal image to aesthetic</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Audio+overview+is+my+personal+favourite</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Audio overview is my personal favourite</t>
+          <t>Online productivity web tool featured in TrickPilot: Convert Normal Image to Aesthetic</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Audio overview is my personal favourite</t>
+          <t>Convert Normal Image to Aesthetic</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/lXYJktKJ-Vc</t>
+          <t>https://www.youtube.com/shorts/p_5KTn8y6oI</t>
         </is>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Boost your PC Performance</t>
+          <t>Cool website</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Boost+your+PC+Performance</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Boost your PC Performance</t>
+          <t>Online productivity web tool featured in TrickPilot: Cool website</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Boost your PC Performance</t>
+          <t>Cool website</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/k2G63P0XQTU</t>
+          <t>https://www.youtube.com/shorts/-qtqbHeYJVQ</t>
         </is>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Build Your Website With JoonWeb</t>
+          <t>Cool website for car lovers</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Build+Your+Website+With+JoonWeb</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Build Your Website With JoonWeb</t>
+          <t>Online productivity web tool featured in TrickPilot: Cool website for car lovers</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Build Your Website With JoonWeb</t>
+          <t>Cool website for car lovers</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/w4e8No8Y8Js</t>
+          <t>https://www.youtube.com/shorts/VUgo4wqyzvs</t>
         </is>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Build your dream PC in seconds</t>
+          <t>Crazy ai tool</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Build+your+dream+PC+in+seconds</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Build your dream PC in seconds</t>
+          <t>Online productivity web tool featured in TrickPilot: Crazy AI Tool</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Build your dream PC in seconds</t>
+          <t>Crazy AI Tool</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/vS9zbNL0gj0</t>
+          <t>https://www.youtube.com/shorts/cpMsLT2_uYM</t>
         </is>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Check Comment for Prompt</t>
+          <t>Description to copy directly</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Check+Comment+for+Prompt</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Check Comment for Prompt</t>
+          <t>Online productivity web tool featured in TrickPilot: Check Description To copy Directly</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Check Comment for Prompt</t>
+          <t>Check Description To copy Directly</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/C5q2TZVHCyI</t>
+          <t>https://www.youtube.com/shorts/JkZ1dYjOLz0</t>
         </is>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Check Description To copy Directly</t>
+          <t>Did you know</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Check+Description+To+copy+Directly</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Check Description To copy Directly</t>
+          <t>Online productivity web tool featured in TrickPilot: Did you know</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Check Description To copy Directly</t>
+          <t>Did you know</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/JkZ1dYjOLz0</t>
+          <t>https://www.youtube.com/shorts/jeSZ6YnUlfg</t>
         </is>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Check if your system supports Windows 11</t>
+          <t>Do not try with your friends</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Check+if+your+system+supports+Windows+11</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Check if your system supports Windows 11</t>
+          <t>Online productivity web tool featured in TrickPilot: Do Not Try With Your Friends</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Check if your system supports Windows 11</t>
+          <t>Do Not Try With Your Friends</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/kEARe449eJU</t>
+          <t>https://www.youtube.com/shorts/RcFhS82Bxio</t>
         </is>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Chinas New Image - Gen Model</t>
+          <t>Dont join gym</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Chinas+New+Image++Gen+Model</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Chinas New Image - Gen Model</t>
+          <t>Online productivity web tool featured in TrickPilot: Dont Join Gym</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Chinas New Image - Gen Model</t>
+          <t>Dont Join Gym</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/x6H0AZF6eq8</t>
+          <t>https://www.youtube.com/shorts/CNEifXDCq_o</t>
         </is>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Claim your Free 1 Year Perplexity Pro</t>
+          <t>Dont send email with boring dp</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Claim+your+Free+1+Year+Perplexity+Pro</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Claim your Free 1 Year Perplexity Pro</t>
+          <t>Online productivity web tool featured in TrickPilot: Dont Send Email With Boring Dp</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Claim your Free 1 Year Perplexity Pro</t>
+          <t>Dont Send Email With Boring Dp</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/6QPWCd41HcI</t>
+          <t>https://www.youtube.com/shorts/w52LksJS9B4</t>
         </is>
       </c>
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Computer Prank To Play On Your Friends</t>
+          <t>Dont try this prank in your school</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Computer+Prank+To+Play+On+Your+Friends</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Computer Prank To Play On Your Friends</t>
+          <t>Online productivity web tool featured in TrickPilot: Dont Try This Prank In Your School</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Computer Prank To Play On Your Friends</t>
+          <t>Dont Try This Prank In Your School</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/fgzyb0WzLFg</t>
+          <t>https://www.youtube.com/shorts/SIogGX92Umg</t>
         </is>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Convert AI to Human</t>
+          <t>Dont use cable for data transfer</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Convert+AI+to+Human</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Convert AI to Human</t>
+          <t>Online productivity web tool featured in TrickPilot: Dont use Cable for Data transfer</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Convert AI to Human</t>
+          <t>Dont use Cable for Data transfer</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/y27EvICFffM</t>
+          <t>https://www.youtube.com/shorts/-Px_H3rrnjQ</t>
         </is>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Convert Normal Image to Aesthetic</t>
+          <t>Dont waste your time</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Convert+Normal+Image+to+Aesthetic</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Convert Normal Image to Aesthetic</t>
+          <t>Online productivity web tool featured in TrickPilot: Dont waste your time</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Convert Normal Image to Aesthetic</t>
+          <t>Dont waste your time</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/p_5KTn8y6oI</t>
+          <t>https://www.youtube.com/shorts/tl4eGJBYr6Q</t>
         </is>
       </c>
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Cool App for student</t>
+          <t xml:space="preserve">Download your aadhaar in emergency </t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Cool+App+for+student</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Cool App for student</t>
+          <t>Online productivity web tool featured in TrickPilot: Download Your Aadhaar In Emergency ! 5 Min Only</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Cool App for student</t>
+          <t>Download Your Aadhaar In Emergency ! 5 Min Only</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/m8SCG3vrNyw</t>
+          <t>https://www.youtube.com/shorts/-nMBe0Lla8Q</t>
         </is>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Cool website</t>
+          <t>E-com with odoo</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Cool+website</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Cool website</t>
+          <t>Online productivity web tool featured in TrickPilot: E-Com With Odoo</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Cool website</t>
+          <t>E-Com With Odoo</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/-qtqbHeYJVQ</t>
+          <t>Read Description</t>
         </is>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Cool website for car lovers</t>
+          <t>Easter eggs in goggle</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Cool+website+for+car+lovers</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Cool website for car lovers</t>
+          <t>Online productivity web tool featured in TrickPilot: Easter Eggs in Goggle</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Cool website for car lovers</t>
+          <t>Easter Eggs in Goggle</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/VUgo4wqyzvs</t>
+          <t>https://www.youtube.com/shorts/FmvOZ8FVv8g</t>
         </is>
       </c>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Crazy AI Tool</t>
+          <t>Edit pdf with ease and accuracy</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Crazy+AI+Tool</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Crazy AI Tool</t>
+          <t>Online productivity web tool featured in TrickPilot: Edit Pdf with ease and accuracy</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>Crazy AI Tool</t>
+          <t>Edit Pdf with ease and accuracy</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/cpMsLT2_uYM</t>
+          <t>https://www.youtube.com/shorts/MclbLfjY_ZQ</t>
         </is>
       </c>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Create Business Website in 4 Steps</t>
+          <t>English speaking</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Create+Business+Website+in+4+Steps</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Create Business Website in 4 Steps</t>
+          <t>Online productivity web tool featured in TrickPilot: Learn English Speaking</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Create Business Website in 4 Steps</t>
+          <t>Learn English Speaking</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/aPxjgiLsMfc</t>
+          <t>https://www.youtube.com/shorts/7MjGhudMZco</t>
         </is>
       </c>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Create Passport Size Photo In Just 2 Min</t>
+          <t>Every tool available to edit pdf</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Create+Passport+Size+Photo+In+Just+2+Min</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Create Passport Size Photo In Just 2 Min</t>
+          <t>Online productivity web tool featured in TrickPilot: Every Tool Available To Edit PDF</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>Create Passport Size Photo In Just 2 Min</t>
+          <t>Every Tool Available To Edit PDF</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/FZVwlYHPlQo</t>
+          <t>https://www.youtube.com/shorts/iIn-mSObTok</t>
         </is>
       </c>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Create Passport Size photos</t>
+          <t>Feeling bored try this</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Create+Passport+Size+photos</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Create Passport Size photos</t>
+          <t>Online productivity web tool featured in TrickPilot: Feeling Bored Try This</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Create Passport Size photos</t>
+          <t>Feeling Bored Try This</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/l598tAICQoI</t>
+          <t>https://www.youtube.com/shorts/c603o4MGi-E</t>
         </is>
       </c>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Create Resume In 2 Mins</t>
+          <t>Fi Money</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Create+Resume+In+2+Mins</t>
+          <t>https://fi.money</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Create Resume In 2 Mins</t>
+          <t>Digital zero-balance banking and smart money management app for students.</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>Create Resume In 2 Mins</t>
+          <t>scam alerts bank account khali hone se bacho</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/iJ17Sr3aukw</t>
+          <t>https://www.youtube.com/shorts/roqvFv5XiqA</t>
         </is>
       </c>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Create web apps in seconds</t>
+          <t>From harvard , anywhere , anytime</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Create+web+apps+in+seconds</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Create web apps in seconds</t>
+          <t>Online productivity web tool featured in TrickPilot: Learn from Harvard , Anywhere , Anytime</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Create web apps in seconds</t>
+          <t>Learn from Harvard , Anywhere , Anytime</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/SgEOtjHEWiA</t>
+          <t>https://www.youtube.com/shorts/oreXJtBZGns</t>
         </is>
       </c>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Did you know</t>
+          <t>GPTExcel</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Did+you+know</t>
+          <t>https://gptexcel.io</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Did you know</t>
+          <t>AI assistant that writes and explains complex Excel, Google Sheets formulas, and SQL.</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Did you know</t>
+          <t>Excel Tips</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/jeSZ6YnUlfg</t>
+          <t>https://www.youtube.com/shorts/zGBMGORdpyA</t>
         </is>
       </c>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Different Way To Lock Your Chat</t>
+          <t>Game - raft</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Different+Way+To+Lock+Your+Chat</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Different Way To Lock Your Chat</t>
+          <t>Online productivity web tool featured in TrickPilot: Game - Raft</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Different Way To Lock Your Chat</t>
+          <t>Game - Raft</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/pMD1J1_3rlg</t>
+          <t>https://www.youtube.com/shorts/L67zsI657ks</t>
         </is>
       </c>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Do Not Try With Your Friends</t>
+          <t>Games to play in browser</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Do+Not+Try+With+Your+Friends</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Do Not Try With Your Friends</t>
+          <t>Online productivity web tool featured in TrickPilot: Games to play in browser</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>Do Not Try With Your Friends</t>
+          <t>Games to play in browser</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/RcFhS82Bxio</t>
+          <t>https://www.youtube.com/shorts/aDnL-v9iRIU</t>
         </is>
       </c>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Dont Join Gym</t>
+          <t>Getting bored try this</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Dont+Join+Gym</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Dont Join Gym</t>
+          <t>Online productivity web tool featured in TrickPilot: Getting Bored Try This</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Dont Join Gym</t>
+          <t>Getting Bored Try This</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/CNEifXDCq_o</t>
+          <t>https://www.youtube.com/shorts/t7MW_T-8wJc</t>
         </is>
       </c>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Dont Send Email With Boring Dp</t>
+          <t>Ghibli style images</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Dont+Send+Email+With+Boring+Dp</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Dont Send Email With Boring Dp</t>
+          <t>Online productivity web tool featured in TrickPilot: Ghibli Style Images</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>Dont Send Email With Boring Dp</t>
+          <t>Ghibli Style Images</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/w52LksJS9B4</t>
+          <t>https://www.youtube.com/shorts/y54anE3ukhg</t>
         </is>
       </c>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Dont Try This Prank In Your School</t>
+          <t>Give your pc z+ security</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Dont+Try+This+Prank+In+Your+School</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Dont Try This Prank In Your School</t>
+          <t>Online productivity web tool featured in TrickPilot: Give Your PC Z+ Security</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Dont Try This Prank In Your School</t>
+          <t>Give Your PC Z+ Security</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/SIogGX92Umg</t>
+          <t>https://www.youtube.com/shorts/5LxWB26Ci74</t>
         </is>
       </c>
     </row>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Dont use Cable for Data transfer</t>
+          <t>Gmail tips</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Dont+use+Cable+for+Data+transfer</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Dont use Cable for Data transfer</t>
+          <t>Online productivity web tool featured in TrickPilot: gmail tips</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>Dont use Cable for Data transfer</t>
+          <t>gmail tips</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/-Px_H3rrnjQ</t>
+          <t>https://www.youtube.com/shorts/w8BfmtPCtLM</t>
         </is>
       </c>
     </row>
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Dont waste your time</t>
+          <t>Gmail tips create template</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Dont+waste+your+time</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Dont waste your time</t>
+          <t>Online productivity web tool featured in TrickPilot: gmail tips create template</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Dont waste your time</t>
+          <t>gmail tips create template</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/tl4eGJBYr6Q</t>
+          <t>https://www.youtube.com/shorts/n_lEBYQU9PM</t>
         </is>
       </c>
     </row>
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Download Your Aadhaar In Emergency ! 5 Min On</t>
+          <t>Gmail tips jo dimak hila de</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Download+Your+Aadhaar+In+Emergency++5+Min+Only</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Download Your Aadhaar In Emergency ! 5 Min Only</t>
+          <t>Online productivity web tool featured in TrickPilot: gmail tips jo dimak hila de</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>Download Your Aadhaar In Emergency ! 5 Min Only</t>
+          <t>gmail tips jo dimak hila de</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/-nMBe0Lla8Q</t>
+          <t>https://www.youtube.com/shorts/HPS-pE0ykho</t>
         </is>
       </c>
     </row>
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>E-Com With Odoo</t>
+          <t>Google search hacks</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=ECom+With+Odoo</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: E-Com With Odoo</t>
+          <t>Online productivity web tool featured in TrickPilot: Google search Hacks</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>E-Com With Odoo</t>
+          <t>Google search Hacks</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>Read Description</t>
+          <t>https://www.youtube.com/shorts/LOrdtU1TtJo</t>
         </is>
       </c>
     </row>
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Easter Eggs in Goggle</t>
+          <t>Googles greatest comeback</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Easter+Eggs+in+Goggle</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Easter Eggs in Goggle</t>
+          <t>Online productivity web tool featured in TrickPilot: Googles Greatest Comeback</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>Easter Eggs in Goggle</t>
+          <t>Googles Greatest Comeback</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/FmvOZ8FVv8g</t>
+          <t>https://www.youtube.com/shorts/Be1T8ZIvTNY</t>
         </is>
       </c>
     </row>
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Edit Pdf with ease and accuracy</t>
+          <t>Goverment website</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Edit+Pdf+with+ease+and+accuracy</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Edit Pdf with ease and accuracy</t>
+          <t>Online productivity web tool featured in TrickPilot: Goverment Website</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Edit Pdf with ease and accuracy</t>
+          <t>Goverment Website</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/MclbLfjY_ZQ</t>
+          <t>https://www.youtube.com/shorts/uQO9eYnnfw4</t>
         </is>
       </c>
     </row>
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Ever thought if switching to linux ? Try this</t>
+          <t>Guaranteed cashback on every recharge</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Ever+thought+if+switching+to+linux++Try+this</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Ever thought if switching to linux ? Try this.</t>
+          <t>Online productivity web tool featured in TrickPilot: Guaranteed Cashback On Every Recharge</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Ever thought if switching to linux ? Try this.</t>
+          <t>Guaranteed Cashback On Every Recharge</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/qJXONJPgH8I</t>
+          <t>https://www.youtube.com/shorts/jlp9G2T5HXY</t>
         </is>
       </c>
     </row>
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Every Tool Available To Edit PDF</t>
+          <t>Hackers can get in your device</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Every+Tool+Available+To+Edit+PDF</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Every Tool Available To Edit PDF</t>
+          <t>Online productivity web tool featured in TrickPilot: Hackers can get in your Device</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Every Tool Available To Edit PDF</t>
+          <t>Hackers can get in your Device</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/iIn-mSObTok</t>
+          <t>https://www.youtube.com/shorts/EPOIJm7E8DM</t>
         </is>
       </c>
     </row>
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Feeling Bored Try This</t>
+          <t>Hard work smart work</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Feeling+Bored+Try+This</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Feeling Bored Try This</t>
+          <t>Online productivity web tool featured in TrickPilot: Hard Work Smart Work</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>Feeling Bored Try This</t>
+          <t>Hard Work Smart Work</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/c603o4MGi-E</t>
+          <t>https://www.youtube.com/shorts/nBfxlojynQs</t>
         </is>
       </c>
     </row>
     <row r="58" ht="22" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Game - Raft</t>
+          <t>Have you ever used camera feature i</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Game++Raft</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Game - Raft</t>
+          <t>Online productivity web tool featured in TrickPilot: Have You Ever Used Camera Feature In Excel</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Game - Raft</t>
+          <t>Have You Ever Used Camera Feature In Excel</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/L67zsI657ks</t>
+          <t>https://www.youtube.com/shorts/E2C9haImd7s</t>
         </is>
       </c>
     </row>
     <row r="59" ht="22" customHeight="1">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Games to play in browser</t>
+          <t>Hollywood is in danger</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Games+to+play+in+browser</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Games to play in browser</t>
+          <t>Online productivity web tool featured in TrickPilot: Hollywood is in Danger</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>Games to play in browser</t>
+          <t>Hollywood is in Danger</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/aDnL-v9iRIU</t>
+          <t>https://www.youtube.com/shorts/RPwINUI793M</t>
         </is>
       </c>
     </row>
     <row r="60" ht="22" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Generate QR For Every Purpose</t>
+          <t>How to customise google doodle</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Generate+QR+For+Every+Purpose</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Generate QR For Every Purpose</t>
+          <t>Online productivity web tool featured in TrickPilot: How to customise Google Doodle</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Generate QR For Every Purpose</t>
+          <t>How to customise Google Doodle</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/Ix9CpUDfBFs</t>
+          <t>https://www.youtube.com/shorts/x9yG1AuZ6H8</t>
         </is>
       </c>
     </row>
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Get 1000s of Live Wallpapers for free</t>
+          <t>How to find movie/webseries source</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Get+1000s+of+Live+Wallpapers+for+free</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Get 1000s of Live Wallpapers for free</t>
+          <t>Online productivity web tool featured in TrickPilot: How To Find Movie/Webseries Source</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>Get 1000s of Live Wallpapers for free</t>
+          <t>How To Find Movie/Webseries Source</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/9r0RVEhOPzI</t>
+          <t>https://www.youtube.com/shorts/j3WWFaWfXG0</t>
         </is>
       </c>
     </row>
     <row r="62" ht="22" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Get 1000s of PNG Images</t>
+          <t>I found 3 useful websites</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Get+1000s+of+PNG+Images</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Get 1000s of PNG Images</t>
+          <t>Online productivity web tool featured in TrickPilot: I found 3 useful websites</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Get 1000s of PNG Images</t>
+          <t>I found 3 useful websites</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/qynUBztz37g</t>
+          <t>https://www.youtube.com/shorts/_JBTKZhpeLw</t>
         </is>
       </c>
     </row>
     <row r="63" ht="22" customHeight="1">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Get 1GB Data Free Anytime</t>
+          <t>If your system supports windows 11</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Get+1GB+Data+Free+Anytime</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Get 1GB Data Free Anytime</t>
+          <t>Online productivity web tool featured in TrickPilot: Check if your system supports Windows 11</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>Get 1GB Data Free Anytime</t>
+          <t>Check if your system supports Windows 11</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/cKHTayk0sUI</t>
+          <t>https://www.youtube.com/shorts/kEARe449eJU</t>
         </is>
       </c>
     </row>
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Get a buisness plan in seconds</t>
+          <t>Import from china</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Get+a+buisness+plan+in+seconds</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Get a buisness plan in seconds</t>
+          <t>Online productivity web tool featured in TrickPilot: Import from China</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Get a buisness plan in seconds</t>
+          <t>Import from China</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/H_A3k_d7txs</t>
+          <t>https://www.youtube.com/shorts/4wwrF3RpCsU</t>
         </is>
       </c>
     </row>
     <row r="65" ht="22" customHeight="1">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Getting Bored Try This</t>
+          <t>Increase pc boot time</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Getting+Bored+Try+This</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Getting Bored Try This</t>
+          <t>Online productivity web tool featured in TrickPilot: Increase PC Boot Time</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>Getting Bored Try This</t>
+          <t>Increase PC Boot Time</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/t7MW_T-8wJc</t>
+          <t>https://www.youtube.com/shorts/UNSyEPXpTwM</t>
         </is>
       </c>
     </row>
     <row r="66" ht="22" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Ghibli Style Images</t>
+          <t>Install this in your pc</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Ghibli+Style+Images</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Ghibli Style Images</t>
+          <t>Online productivity web tool featured in TrickPilot: Install this in your PC</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Ghibli Style Images</t>
+          <t>Install this in your PC</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/y54anE3ukhg</t>
+          <t>https://www.youtube.com/shorts/1P1R1T5Tsno</t>
         </is>
       </c>
     </row>
     <row r="67" ht="22" customHeight="1">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Give Your PC Z+ Security</t>
+          <t>Invoice with odoo</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Give+Your+PC+Z+Security</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Give Your PC Z+ Security</t>
+          <t>Online productivity web tool featured in TrickPilot: Make Invoice with odoo</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>Give Your PC Z+ Security</t>
+          <t>Make Invoice with odoo</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/5LxWB26Ci74</t>
+          <t>https://www.youtube.com/shorts/VUWSS-QPcTg</t>
         </is>
       </c>
     </row>
     <row r="68" ht="22" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Google search Hacks</t>
+          <t>Iphone 17</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Google+search+Hacks</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Google search Hacks</t>
+          <t>Online productivity web tool featured in TrickPilot: Iphone 17</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Google search Hacks</t>
+          <t>Iphone 17</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/LOrdtU1TtJo</t>
+          <t>https://www.youtube.com/shorts/5ZwGdTioKRE</t>
         </is>
       </c>
     </row>
     <row r="69" ht="22" customHeight="1">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Google search trick for Students</t>
+          <t>Iphone tricks</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Google+search+trick+for+Students</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Google search trick for Students</t>
+          <t>Online productivity web tool featured in TrickPilot: Iphone tricks</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>Google search trick for Students</t>
+          <t>Iphone tricks</t>
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/C2Ardr1bZ40</t>
+          <t>https://www.youtube.com/shorts/mOIM6IAyDcI</t>
         </is>
       </c>
     </row>
     <row r="70" ht="22" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Googles Greatest Comeback</t>
+          <t>Iphones tips</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Googles+Greatest+Comeback</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Googles Greatest Comeback</t>
+          <t>Online productivity web tool featured in TrickPilot: iPhones tips</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Googles Greatest Comeback</t>
+          <t>iPhones tips</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/Be1T8ZIvTNY</t>
+          <t>https://www.youtube.com/shorts/PBpEO6XmN68</t>
         </is>
       </c>
     </row>
     <row r="71" ht="22" customHeight="1">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Goverment Website</t>
+          <t>Its called +addressing</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Goverment+Website</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Goverment Website</t>
+          <t>Online productivity web tool featured in TrickPilot: Its called +Addressing</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>Goverment Website</t>
+          <t>Its called +Addressing</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/uQO9eYnnfw4</t>
+          <t>https://www.youtube.com/shorts/L6uzPDWyLkg</t>
         </is>
       </c>
     </row>
     <row r="72" ht="22" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Guaranteed Cashback On Every Recharge</t>
+          <t>Its just launched and its so perfect</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Guaranteed+Cashback+On+Every+Recharge</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Guaranteed Cashback On Every Recharge</t>
+          <t>Online productivity web tool featured in TrickPilot: Its just launched and its so perfect</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Guaranteed Cashback On Every Recharge</t>
+          <t>Its just launched and its so perfect</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/jlp9G2T5HXY</t>
+          <t>https://www.youtube.com/shorts/wjkgZ1GsvRw</t>
         </is>
       </c>
     </row>
     <row r="73" ht="22" customHeight="1">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Hackers can get in your Device</t>
+          <t>Just 1 website for all ai tools</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Hackers+can+get+in+your+Device</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Hackers can get in your Device</t>
+          <t>Online productivity web tool featured in TrickPilot: Just 1 Website For All AI Tools</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>Hackers can get in your Device</t>
+          <t>Just 1 Website For All AI Tools</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/EPOIJm7E8DM</t>
+          <t>https://www.youtube.com/shorts/bo77yxNyLnY</t>
         </is>
       </c>
     </row>
     <row r="74" ht="22" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Hard Work Smart Work</t>
+          <t>Just forget your laptop webcam</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Hard+Work+Smart+Work</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Hard Work Smart Work</t>
+          <t>Online productivity web tool featured in TrickPilot: Just Forget Your Laptop Webcam</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Hard Work Smart Work</t>
+          <t>Just Forget Your Laptop Webcam</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/nBfxlojynQs</t>
+          <t>https://www.youtube.com/shorts/JT4jja1nMK0</t>
         </is>
       </c>
     </row>
     <row r="75" ht="22" customHeight="1">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Have You Ever Used Camera Feature In Excel</t>
+          <t>Know what your laptop is capable of</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Have+You+Ever+Used+Camera+Feature+In+Excel</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Have You Ever Used Camera Feature In Excel</t>
+          <t>Online productivity web tool featured in TrickPilot: Know What your laptop is capable of</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>Have You Ever Used Camera Feature In Excel</t>
+          <t>Know What your laptop is capable of</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/E2C9haImd7s</t>
+          <t>https://www.youtube.com/shorts/2cDuAbLHfic</t>
         </is>
       </c>
     </row>
     <row r="76" ht="22" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Hollywood is in Danger</t>
+          <t>Kuch aisa dhundh rha hu jisse bilku</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Hollywood+is+in+Danger</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Hollywood is in Danger</t>
+          <t>Online productivity web tool featured in TrickPilot: Kuch aisa dhundh rha hu jisse bilkul padhna hi na pade - Bane rho dosto channel pe</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Hollywood is in Danger</t>
+          <t>Kuch aisa dhundh rha hu jisse bilkul padhna hi na pade - Bane rho dosto channel pe</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/RPwINUI793M</t>
+          <t>https://www.youtube.com/shorts/KzPRBcveNwQ</t>
         </is>
       </c>
     </row>
     <row r="77" ht="22" customHeight="1">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>How To Find Movie/Webseries Source</t>
+          <t>Launch your own e-commerce store</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=How+To+Find+MovieWebseries+Source</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: How To Find Movie/Webseries Source</t>
+          <t>Online productivity web tool featured in TrickPilot: Launch your own E-Commerce Store</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>How To Find Movie/Webseries Source</t>
+          <t>Launch your own E-Commerce Store</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/j3WWFaWfXG0</t>
+          <t>https://www.youtube.com/shorts/OBFLsyqS57U</t>
         </is>
       </c>
     </row>
     <row r="78" ht="22" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>How to Create Passport Size Photo</t>
+          <t>Link in bio :</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=How+to+Create+Passport+Size+Photo</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: How to Create Passport Size Photo</t>
+          <t>Online productivity web tool featured in TrickPilot: Link In Bio :</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>How to Create Passport Size Photo</t>
+          <t>Link In Bio :</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/mjzc-LwJY-U</t>
+          <t>https://www.youtube.com/shorts/354fSOFN1t0</t>
         </is>
       </c>
     </row>
     <row r="79" ht="22" customHeight="1">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>How to customise Google Doodle</t>
+          <t>Lovart nano banana = creativity wit</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=How+to+customise+Google+Doodle</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: How to customise Google Doodle</t>
+          <t>Online productivity web tool featured in TrickPilot: Lovart Nano Banana = creativity without limits</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>How to customise Google Doodle</t>
+          <t>Lovart Nano Banana = creativity without limits</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/x9yG1AuZ6H8</t>
+          <t>https://www.youtube.com/shorts/ItK87jJfWYE</t>
         </is>
       </c>
     </row>
     <row r="80" ht="22" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>How to edit photo in one click</t>
+          <t>Make 3d website in just 5 min for y</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=How+to+edit+photo+in+one+click</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: How to edit photo in one click</t>
+          <t>Online productivity web tool featured in TrickPilot: Make 3D Website In Just 5 Min For Your Business</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>How to edit photo in one click</t>
+          <t>Make 3D Website In Just 5 Min For Your Business</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/dSf2xBDgmrE</t>
+          <t>https://www.youtube.com/shorts/wDPBfOqTayk</t>
         </is>
       </c>
     </row>
     <row r="81" ht="22" customHeight="1">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>I found 3 useful websites</t>
+          <t>Make your presentation attractive u</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=I+found+3+useful+websites</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: I found 3 useful websites</t>
+          <t>Online productivity web tool featured in TrickPilot: Make Your Presentation Attractive Using 3 Websites</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>I found 3 useful websites</t>
+          <t>Make Your Presentation Attractive Using 3 Websites</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/_JBTKZhpeLw</t>
+          <t>https://www.youtube.com/shorts/UK0Wjizv9H8</t>
         </is>
       </c>
     </row>
     <row r="82" ht="22" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Import from China</t>
+          <t>Most powerful ai of 2025</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Import+from+China</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Import from China</t>
+          <t>Online productivity web tool featured in TrickPilot: Most powerful Ai of 2025</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Import from China</t>
+          <t>Most powerful Ai of 2025</t>
         </is>
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/4wwrF3RpCsU</t>
+          <t>https://www.youtube.com/shorts/ec4ean-hbkI</t>
         </is>
       </c>
     </row>
     <row r="83" ht="22" customHeight="1">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Increase PC Boot Time</t>
+          <t>Multiplayer games to play with friends</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Increase+PC+Boot+Time</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Increase PC Boot Time</t>
+          <t>Online productivity web tool featured in TrickPilot: Multiplayer Games to play with friends</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>Increase PC Boot Time</t>
+          <t>Multiplayer Games to play with friends</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/UNSyEPXpTwM</t>
+          <t>https://www.youtube.com/shorts/1Yvl9s4eOJQ</t>
         </is>
       </c>
     </row>
     <row r="84" ht="22" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Install this in your PC</t>
+          <t>Nano banana is seriously crazy</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Install+this+in+your+PC</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Install this in your PC</t>
+          <t>Online productivity web tool featured in TrickPilot: Nano Banana is seriously crazy</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Install this in your PC</t>
+          <t>Nano Banana is seriously crazy</t>
         </is>
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/1P1R1T5Tsno</t>
+          <t>https://www.youtube.com/shorts/Y49wHDP_hRM</t>
         </is>
       </c>
     </row>
     <row r="85" ht="22" customHeight="1">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Iphone 17</t>
+          <t>Nano banana pro</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Iphone+17</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Iphone 17</t>
+          <t>Online productivity web tool featured in TrickPilot: Nano Banana Pro</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>Iphone 17</t>
+          <t>Nano Banana Pro</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/5ZwGdTioKRE</t>
+          <t>https://www.youtube.com/shorts/WAYAI-sJtU8</t>
         </is>
       </c>
     </row>
     <row r="86" ht="22" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Iphone tricks</t>
+          <t>Nano pro is seriously impressive</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Iphone+tricks</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Iphone tricks</t>
+          <t>Online productivity web tool featured in TrickPilot: Nano Pro is Seriously impressive</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Iphone tricks</t>
+          <t>Nano Pro is Seriously impressive</t>
         </is>
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/mOIM6IAyDcI</t>
+          <t>https://www.youtube.com/shorts/OpJHHDUmmvw</t>
         </is>
       </c>
     </row>
     <row r="87" ht="22" customHeight="1">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Its called +Addressing</t>
+          <t>New update in google flow</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Its+called+Addressing</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Its called +Addressing</t>
+          <t>Online productivity web tool featured in TrickPilot: New Update in Google Flow</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>Its called +Addressing</t>
+          <t>New Update in Google Flow</t>
         </is>
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/L6uzPDWyLkg</t>
+          <t>https://www.youtube.com/shorts/6Inyvt3bV9s</t>
         </is>
       </c>
     </row>
     <row r="88" ht="22" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Just 1 Website For All AI Tools</t>
+          <t>No more fantasy gaming</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Just+1+Website+For+All+AI+Tools</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Just 1 Website For All AI Tools</t>
+          <t>Online productivity web tool featured in TrickPilot: No more fantasy gaming</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Just 1 Website For All AI Tools</t>
+          <t>No more fantasy gaming</t>
         </is>
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/bo77yxNyLnY</t>
+          <t>https://www.youtube.com/shorts/tXwH3qJ3GSU</t>
         </is>
       </c>
     </row>
     <row r="89" ht="22" customHeight="1">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Just Forget Your Laptop Webcam</t>
+          <t>Not for kids</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Just+Forget+Your+Laptop+Webcam</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Just Forget Your Laptop Webcam</t>
+          <t>Online productivity web tool featured in TrickPilot: Not For Kids</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>Just Forget Your Laptop Webcam</t>
+          <t>Not For Kids</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/JT4jja1nMK0</t>
+          <t>https://www.youtube.com/shorts/ksHGRxhTzH8</t>
         </is>
       </c>
     </row>
     <row r="90" ht="22" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Know What your laptop is capable of</t>
+          <t>Nothing to be afraid of</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Know+What+your+laptop+is+capable+of</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Know What your laptop is capable of</t>
+          <t>Online productivity web tool featured in TrickPilot: Nothing to be afraid of</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Know What your laptop is capable of</t>
+          <t>Nothing to be afraid of</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/2cDuAbLHfic</t>
+          <t>https://www.youtube.com/shorts/0Eyah32WSfQ</t>
         </is>
       </c>
     </row>
     <row r="91" ht="22" customHeight="1">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Kuch aisa dhundh rha hu jisse bilkul padhna h</t>
+          <t>Now chat with your large pdf in eng</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Kuch+aisa+dhundh+rha+hu+jisse+bilkul+padhna+hi+na+pade++Bane+rho+dosto+channel+pe</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Kuch aisa dhundh rha hu jisse bilkul padhna hi na pade - Bane rho dosto channel pe</t>
+          <t>Online productivity web tool featured in TrickPilot: Now Chat With Your Large PDF In English &amp; Hindi</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>Kuch aisa dhundh rha hu jisse bilkul padhna hi na pade - Bane rho dosto channel pe</t>
+          <t>Now Chat With Your Large PDF In English &amp; Hindi</t>
         </is>
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/KzPRBcveNwQ</t>
+          <t>https://www.youtube.com/shorts/Bjq31ujNRVg</t>
         </is>
       </c>
     </row>
     <row r="92" ht="22" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Launch your own E-Commerce Store</t>
+          <t>One of the best extension</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Launch+your+own+ECommerce+Store</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Launch your own E-Commerce Store</t>
+          <t>Online productivity web tool featured in TrickPilot: One of the best Extension</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Launch your own E-Commerce Store</t>
+          <t>One of the best Extension</t>
         </is>
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/OBFLsyqS57U</t>
+          <t>https://www.youtube.com/shorts/ueaz5Y6hzpA</t>
         </is>
       </c>
     </row>
     <row r="93" ht="22" customHeight="1">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Learn English Speaking</t>
+          <t>One of the best tool for windows pcs</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Learn+English+Speaking</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Learn English Speaking</t>
+          <t>Online productivity web tool featured in TrickPilot: One of the best tool for Windows PCs</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>Learn English Speaking</t>
+          <t>One of the best tool for Windows PCs</t>
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/7MjGhudMZco</t>
+          <t>https://www.youtube.com/shorts/hWJyc4F0eb4</t>
         </is>
       </c>
     </row>
     <row r="94" ht="22" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Learn from Harvard , Anywhere , Anytime</t>
+          <t>Only tool you need for writing</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Learn+from+Harvard++Anywhere++Anytime</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Learn from Harvard , Anywhere , Anytime</t>
+          <t>Online productivity web tool featured in TrickPilot: Only Tool You need For Writing</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Learn from Harvard , Anywhere , Anytime</t>
+          <t>Only Tool You need For Writing</t>
         </is>
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/oreXJtBZGns</t>
+          <t>https://www.youtube.com/shorts/J5cQYmQz8wc</t>
         </is>
       </c>
     </row>
     <row r="95" ht="22" customHeight="1">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>Link In Bio :</t>
+          <t>Pc tips</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Link+In+Bio</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Link In Bio :</t>
+          <t>Online productivity web tool featured in TrickPilot: Pc Tips</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>Link In Bio :</t>
+          <t>Pc Tips</t>
         </is>
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/354fSOFN1t0</t>
+          <t>https://www.youtube.com/shorts/0FSiIHCj3cE</t>
         </is>
       </c>
     </row>
     <row r="96" ht="22" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Lovart Nano Banana = creativity without limit</t>
+          <t>Pc tips (part 30)</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Lovart+Nano+Banana++creativity+without+limits</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Lovart Nano Banana = creativity without limits</t>
+          <t>Online productivity web tool featured in TrickPilot: PC Tips (Part 30)</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Lovart Nano Banana = creativity without limits</t>
+          <t>PC Tips (Part 30)</t>
         </is>
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/ItK87jJfWYE</t>
+          <t>https://www.youtube.com/shorts/UyF4FmUjS5A</t>
         </is>
       </c>
     </row>
     <row r="97" ht="22" customHeight="1">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Make Invoice with odoo</t>
+          <t>Pc tips ab hogi har problem solve</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Make+Invoice+with+odoo</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Make Invoice with odoo</t>
+          <t>Online productivity web tool featured in TrickPilot: PC tips Ab hogi har problem solve</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>Make Invoice with odoo</t>
+          <t>PC tips Ab hogi har problem solve</t>
         </is>
       </c>
       <c r="F97" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/VUWSS-QPcTg</t>
+          <t>https://www.youtube.com/shorts/AF4wuTFgOLo</t>
         </is>
       </c>
     </row>
     <row r="98" ht="22" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Make Profile Pictures Attractive</t>
+          <t xml:space="preserve">Pc tips ab hogi pdf se related har </t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Make+Profile+Pictures+Attractive</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Make Profile Pictures Attractive</t>
+          <t>Online productivity web tool featured in TrickPilot: PC tips Ab hogi Pdf se related har problem solved</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Make Profile Pictures Attractive</t>
+          <t>PC tips Ab hogi Pdf se related har problem solved</t>
         </is>
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/W965cfULTCo</t>
+          <t>https://www.youtube.com/shorts/-TvsmYMT4S8</t>
         </is>
       </c>
     </row>
     <row r="99" ht="22" customHeight="1">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>Make Your Presentation Attractive Using 3 Web</t>
+          <t>Pc tips ab koi hack nai kar payga</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Make+Your+Presentation+Attractive+Using+3+Websites</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Make Your Presentation Attractive Using 3 Websites</t>
+          <t>Online productivity web tool featured in TrickPilot: pc tips ab koi hack nai kar payga</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>Make Your Presentation Attractive Using 3 Websites</t>
+          <t>pc tips ab koi hack nai kar payga</t>
         </is>
       </c>
       <c r="F99" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/UK0Wjizv9H8</t>
+          <t>https://www.youtube.com/shorts/Kif7ARVC38M</t>
         </is>
       </c>
     </row>
     <row r="100" ht="22" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Most powerful Ai of 2025</t>
+          <t>Pc tips access your files anywhere</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Most+powerful+Ai+of+2025</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Most powerful Ai of 2025</t>
+          <t>Online productivity web tool featured in TrickPilot: pc tips access your files anywhere</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>Most powerful Ai of 2025</t>
+          <t>pc tips access your files anywhere</t>
         </is>
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/ec4ean-hbkI</t>
+          <t>https://www.youtube.com/shorts/uuVth_awCoc</t>
         </is>
       </c>
     </row>
     <row r="101" ht="22" customHeight="1">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>Multiplayer Games to play with friends</t>
+          <t>Pc tips change your boring desktop</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Multiplayer+Games+to+play+with+friends</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Multiplayer Games to play with friends</t>
+          <t>Online productivity web tool featured in TrickPilot: pc tips change your boring desktop</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>Multiplayer Games to play with friends</t>
+          <t>pc tips change your boring desktop</t>
         </is>
       </c>
       <c r="F101" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/1Yvl9s4eOJQ</t>
+          <t>https://www.youtube.com/shorts/fIYtXAHDJ4M</t>
         </is>
       </c>
     </row>
     <row r="102" ht="22" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Nano Banana Pro</t>
+          <t>Pc tips find anything in your pc</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Nano+Banana+Pro</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Nano Banana Pro</t>
+          <t>Online productivity web tool featured in TrickPilot: PC tips Find anything in your PC</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>Nano Banana Pro</t>
+          <t>PC tips Find anything in your PC</t>
         </is>
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/WAYAI-sJtU8</t>
+          <t>https://www.youtube.com/shorts/Vt9BhZ7fSd4</t>
         </is>
       </c>
     </row>
     <row r="103" ht="22" customHeight="1">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Nano Banana is seriously crazy</t>
+          <t>Pc tips kahi apka pc hack to nai</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Nano+Banana+is+seriously+crazy</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Nano Banana is seriously crazy</t>
+          <t>Online productivity web tool featured in TrickPilot: PC tips Kahi apka pc hack to nai</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>Nano Banana is seriously crazy</t>
+          <t>PC tips Kahi apka pc hack to nai</t>
         </is>
       </c>
       <c r="F103" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/Y49wHDP_hRM</t>
+          <t>https://www.youtube.com/shorts/n2QHeJIKsdU</t>
         </is>
       </c>
     </row>
     <row r="104" ht="22" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Nano Pro is Seriously impressive</t>
+          <t>Pc tips mobile game khelo ab pc mein</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Nano+Pro+is+Seriously+impressive</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Nano Pro is Seriously impressive</t>
+          <t>Online productivity web tool featured in TrickPilot: pc tips mobile game khelo ab pc mein</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>Nano Pro is Seriously impressive</t>
+          <t>pc tips mobile game khelo ab pc mein</t>
         </is>
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/OpJHHDUmmvw</t>
+          <t>https://www.youtube.com/shorts/Z67GqoZ59RA</t>
         </is>
       </c>
     </row>
     <row r="105" ht="22" customHeight="1">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>New Update in Google Flow</t>
+          <t>Pc tips open bios directly</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=New+Update+in+Google+Flow</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: New Update in Google Flow</t>
+          <t>Online productivity web tool featured in TrickPilot: pc tips open bios directly</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>New Update in Google Flow</t>
+          <t>pc tips open bios directly</t>
         </is>
       </c>
       <c r="F105" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/6Inyvt3bV9s</t>
+          <t>https://www.youtube.com/shorts/Aa_TzaEdDKQ</t>
         </is>
       </c>
     </row>
     <row r="106" ht="22" customHeight="1">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>No more fantasy gaming</t>
+          <t xml:space="preserve">Pc tips powerful website that make </t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=No+more+fantasy+gaming</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: No more fantasy gaming</t>
+          <t>Online productivity web tool featured in TrickPilot: PC tips powerful website that make your life easy</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>No more fantasy gaming</t>
+          <t>PC tips powerful website that make your life easy</t>
         </is>
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/tXwH3qJ3GSU</t>
+          <t>https://www.youtube.com/shorts/3DftSWUK5DU</t>
         </is>
       </c>
     </row>
     <row r="107" ht="22" customHeight="1">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>No relatives, only robots</t>
+          <t>Pc tips sabhi problams ka solution</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=No+relatives+only+robots</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: No relatives, only robots</t>
+          <t>Online productivity web tool featured in TrickPilot: pc tips sabhi problams ka solution</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>No relatives, only robots</t>
+          <t>pc tips sabhi problams ka solution</t>
         </is>
       </c>
       <c r="F107" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/WURbOfN2aOE</t>
+          <t>https://www.youtube.com/shorts/cb2SgUgUbww</t>
         </is>
       </c>
     </row>
     <row r="108" ht="22" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Not For Kids</t>
+          <t>Pc tips storage ki problem solve</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Not+For+Kids</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Not For Kids</t>
+          <t>Online productivity web tool featured in TrickPilot: PC Tips Storage Ki problem solve</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>Not For Kids</t>
+          <t>PC Tips Storage Ki problem solve</t>
         </is>
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/ksHGRxhTzH8</t>
+          <t>https://www.youtube.com/shorts/Bq2agaja3p4</t>
         </is>
       </c>
     </row>
     <row r="109" ht="22" customHeight="1">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>Nothing to be afraid of</t>
+          <t>Pc tipsab chalega pehle se fast</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Nothing+to+be+afraid+of</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Nothing to be afraid of</t>
+          <t>Online productivity web tool featured in TrickPilot: PC TipsAb chalega pehle se Fast</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>Nothing to be afraid of</t>
+          <t>PC TipsAb chalega pehle se Fast</t>
         </is>
       </c>
       <c r="F109" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/0Eyah32WSfQ</t>
+          <t>https://www.youtube.com/shorts/gEu-9L48G7M</t>
         </is>
       </c>
     </row>
     <row r="110" ht="22" customHeight="1">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Now Chat With Your Large PDF In English &amp; Hin</t>
+          <t>Pc tipsand hack</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Now+Chat+With+Your+Large+PDF+In+English++Hindi</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Now Chat With Your Large PDF In English &amp; Hindi</t>
+          <t>Online productivity web tool featured in TrickPilot: pc tipsand hack</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>Now Chat With Your Large PDF In English &amp; Hindi</t>
+          <t>pc tipsand hack</t>
         </is>
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/Bjq31ujNRVg</t>
+          <t>https://www.youtube.com/shorts/1RzEFV4bzuw</t>
         </is>
       </c>
     </row>
     <row r="111" ht="22" customHeight="1">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>One of the best Extension</t>
+          <t xml:space="preserve">Pc tipsand hack gmail tips protect </t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=One+of+the+best+Extension</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: One of the best Extension</t>
+          <t>Online productivity web tool featured in TrickPilot: pc tipsand hack Gmail Tips Protect your email</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>One of the best Extension</t>
+          <t>pc tipsand hack Gmail Tips Protect your email</t>
         </is>
       </c>
       <c r="F111" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/ueaz5Y6hzpA</t>
+          <t>https://www.youtube.com/shorts/UAY-uHYXMeU</t>
         </is>
       </c>
     </row>
     <row r="112" ht="22" customHeight="1">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>One of the best tool for Windows PCs</t>
+          <t>Pc tricks</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=One+of+the+best+tool+for+Windows+PCs</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: One of the best tool for Windows PCs</t>
+          <t>Online productivity web tool featured in TrickPilot: Pc Tricks</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>One of the best tool for Windows PCs</t>
+          <t>Pc Tricks</t>
         </is>
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/hWJyc4F0eb4</t>
+          <t>https://www.youtube.com/shorts/thODn-cH8Z0</t>
         </is>
       </c>
     </row>
     <row r="113" ht="22" customHeight="1">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>Only Tool You need For Writing</t>
+          <t>Planning to join gym ? watch this</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Only+Tool+You+need+For+Writing</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Only Tool You need For Writing</t>
+          <t>Online productivity web tool featured in TrickPilot: Planning to join Gym ? Watch this</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>Only Tool You need For Writing</t>
+          <t>Planning to join Gym ? Watch this</t>
         </is>
       </c>
       <c r="F113" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/J5cQYmQz8wc</t>
+          <t>https://www.youtube.com/shorts/Q58ocHlAVKA</t>
         </is>
       </c>
     </row>
     <row r="114" ht="22" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>PC Tips (Part 30)</t>
+          <t>Play minecraft in browser</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=PC+Tips+Part+30</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: PC Tips (Part 30)</t>
+          <t>Online productivity web tool featured in TrickPilot: Play Minecraft In Browser</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>PC Tips (Part 30)</t>
+          <t>Play Minecraft In Browser</t>
         </is>
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/UyF4FmUjS5A</t>
+          <t>https://www.youtube.com/shorts/5P5CqPAM55w</t>
         </is>
       </c>
     </row>
     <row r="115" ht="22" customHeight="1">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>PC Tips Storage Ki problem solve</t>
+          <t>Powerful extension</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=PC+Tips+Storage+Ki+problem+solve</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: PC Tips Storage Ki problem solve</t>
+          <t>Online productivity web tool featured in TrickPilot: powerful extension</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>PC Tips Storage Ki problem solve</t>
+          <t>powerful extension</t>
         </is>
       </c>
       <c r="F115" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/Bq2agaja3p4</t>
+          <t>https://www.youtube.com/shorts/oV034iwOpgA</t>
         </is>
       </c>
     </row>
     <row r="116" ht="22" customHeight="1">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>PC TipsAb chalega pehle se Fast</t>
+          <t>Powerful website</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=PC+TipsAb+chalega+pehle+se+Fast</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: PC TipsAb chalega pehle se Fast</t>
+          <t>Online productivity web tool featured in TrickPilot: powerful website</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>PC TipsAb chalega pehle se Fast</t>
+          <t>powerful website</t>
         </is>
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/gEu-9L48G7M</t>
+          <t>https://www.youtube.com/shorts/4tjNhjE3iSk</t>
         </is>
       </c>
     </row>
     <row r="117" ht="22" customHeight="1">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>PC tips Ab hogi Pdf se related har problem so</t>
+          <t>Powerful website for fun</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=PC+tips+Ab+hogi+Pdf+se+related+har+problem+solved</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: PC tips Ab hogi Pdf se related har problem solved</t>
+          <t>Online productivity web tool featured in TrickPilot: Powerful website for fun</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>PC tips Ab hogi Pdf se related har problem solved</t>
+          <t>Powerful website for fun</t>
         </is>
       </c>
       <c r="F117" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/-TvsmYMT4S8</t>
+          <t>https://www.youtube.com/shorts/f9MJtl7whg8</t>
         </is>
       </c>
     </row>
     <row r="118" ht="22" customHeight="1">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>PC tips Ab hogi har problem solve</t>
+          <t>Powerful websites (part 20)</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=PC+tips+Ab+hogi+har+problem+solve</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: PC tips Ab hogi har problem solve</t>
+          <t>Online productivity web tool featured in TrickPilot: Powerful Websites (Part 20)</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>PC tips Ab hogi har problem solve</t>
+          <t>Powerful Websites (Part 20)</t>
         </is>
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/AF4wuTFgOLo</t>
+          <t>https://www.youtube.com/shorts/AzSnEeNlRdA</t>
         </is>
       </c>
     </row>
     <row r="119" ht="22" customHeight="1">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>PC tips Find anything in your PC</t>
+          <t>Profile pictures attractive</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=PC+tips+Find+anything+in+your+PC</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: PC tips Find anything in your PC</t>
+          <t>Online productivity web tool featured in TrickPilot: Make Profile Pictures Attractive</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>PC tips Find anything in your PC</t>
+          <t>Make Profile Pictures Attractive</t>
         </is>
       </c>
       <c r="F119" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/Vt9BhZ7fSd4</t>
+          <t>https://www.youtube.com/shorts/W965cfULTCo</t>
         </is>
       </c>
     </row>
     <row r="120" ht="22" customHeight="1">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>PC tips Kahi apka pc hack to nai</t>
+          <t xml:space="preserve">Public ka trust permanently damage </t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=PC+tips+Kahi+apka+pc+hack+to+nai</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: PC tips Kahi apka pc hack to nai</t>
+          <t>Online productivity web tool featured in TrickPilot: Public ka trust permanently damage hone wala hai</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>PC tips Kahi apka pc hack to nai</t>
+          <t>Public ka trust permanently damage hone wala hai</t>
         </is>
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/n2QHeJIKsdU</t>
+          <t>https://www.youtube.com/shorts/QexwB6ib9TY</t>
         </is>
       </c>
     </row>
     <row r="121" ht="22" customHeight="1">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PC tips powerful website that make your life </t>
+          <t>Qr for every purpose</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=PC+tips+powerful+website+that+make+your+life+easy</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: PC tips powerful website that make your life easy</t>
+          <t>Online productivity web tool featured in TrickPilot: Generate QR For Every Purpose</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>PC tips powerful website that make your life easy</t>
+          <t>Generate QR For Every Purpose</t>
         </is>
       </c>
       <c r="F121" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/3DftSWUK5DU</t>
+          <t>https://www.youtube.com/shorts/Ix9CpUDfBFs</t>
         </is>
       </c>
     </row>
     <row r="122" ht="22" customHeight="1">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Pc Tips</t>
+          <t>Reactive Resume</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Pc+Tips</t>
+          <t>https://rxresu.me</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Pc Tips</t>
+          <t>Free, open-source, privacy-focused resume builder with customizable layouts and PDF export.</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>Pc Tips</t>
+          <t>Create Resume In 2 Mins</t>
         </is>
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/0FSiIHCj3cE</t>
+          <t>https://www.youtube.com/shorts/iJ17Sr3aukw</t>
         </is>
       </c>
     </row>
     <row r="123" ht="22" customHeight="1">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>Pc Tricks</t>
+          <t>Remove hacker from your pc</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Pc+Tricks</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Pc Tricks</t>
+          <t>Online productivity web tool featured in TrickPilot: Remove Hacker from your PC</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>Pc Tricks</t>
+          <t>Remove Hacker from your PC</t>
         </is>
       </c>
       <c r="F123" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/thODn-cH8Z0</t>
+          <t>https://www.youtube.com/shorts/g55fG2oPByo</t>
         </is>
       </c>
     </row>
     <row r="124" ht="22" customHeight="1">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Planning to join Gym ? Watch this</t>
+          <t xml:space="preserve">Remove your gmail id from unwanted </t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Planning+to+join+Gym++Watch+this</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Planning to join Gym ? Watch this</t>
+          <t>Online productivity web tool featured in TrickPilot: Remove Your Gmail Id From Unwanted Website</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>Planning to join Gym ? Watch this</t>
+          <t>Remove Your Gmail Id From Unwanted Website</t>
         </is>
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/Q58ocHlAVKA</t>
+          <t>https://www.youtube.com/shorts/9QD7cxwr3Yk</t>
         </is>
       </c>
     </row>
     <row r="125" ht="22" customHeight="1">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>Play Minecraft In Browser</t>
+          <t>Safety tips</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Play+Minecraft+In+Browser</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Play Minecraft In Browser</t>
+          <t>Online productivity web tool featured in TrickPilot: Safety Tips</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>Play Minecraft In Browser</t>
+          <t>Safety Tips</t>
         </is>
       </c>
       <c r="F125" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/5P5CqPAM55w</t>
+          <t>https://www.youtube.com/shorts/CozH9RSszMk</t>
         </is>
       </c>
     </row>
     <row r="126" ht="22" customHeight="1">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Powerful Websites (Part 20)</t>
+          <t>Samajh nhi aa rha caption kya dalu</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Powerful+Websites+Part+20</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Powerful Websites (Part 20)</t>
+          <t>Online productivity web tool featured in TrickPilot: Samajh nhi aa rha caption kya dalu</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>Powerful Websites (Part 20)</t>
+          <t>Samajh nhi aa rha caption kya dalu</t>
         </is>
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/AzSnEeNlRdA</t>
+          <t>https://www.youtube.com/shorts/sXubpOO59I4</t>
         </is>
       </c>
     </row>
     <row r="127" ht="22" customHeight="1">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>Powerful website for fun</t>
+          <t>Save these hacks for your pc</t>
         </is>
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Powerful+website+for+fun</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Powerful website for fun</t>
+          <t>Online productivity web tool featured in TrickPilot: Save these hacks for your PC</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>Powerful website for fun</t>
+          <t>Save these hacks for your PC</t>
         </is>
       </c>
       <c r="F127" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/f9MJtl7whg8</t>
+          <t>https://www.youtube.com/shorts/UkxHlxE5ZFI</t>
         </is>
       </c>
     </row>
     <row r="128" ht="22" customHeight="1">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Public ka trust permanently damage hone wala </t>
+          <t>Save this 4-step formula</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Public+ka+trust+permanently+damage+hone+wala+hai</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Public ka trust permanently damage hone wala hai</t>
+          <t>Online productivity web tool featured in TrickPilot: Save this 4-step formula</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>Public ka trust permanently damage hone wala hai</t>
+          <t>Save this 4-step formula</t>
         </is>
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/QexwB6ib9TY</t>
+          <t>CHAT GPT</t>
         </is>
       </c>
     </row>
     <row r="129" ht="22" customHeight="1">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>Remove Hacker from your PC</t>
+          <t>Save this for kids</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Remove+Hacker+from+your+PC</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Remove Hacker from your PC</t>
+          <t>Online productivity web tool featured in TrickPilot: Save this for Kids</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>Remove Hacker from your PC</t>
+          <t>Save this for Kids</t>
         </is>
       </c>
       <c r="F129" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/g55fG2oPByo</t>
+          <t>https://www.youtube.com/shorts/zFyDgq1nMgw</t>
         </is>
       </c>
     </row>
     <row r="130" ht="22" customHeight="1">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Remove Your Gmail Id From Unwanted Website</t>
+          <t>Save this if you play games</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Remove+Your+Gmail+Id+From+Unwanted+Website</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Remove Your Gmail Id From Unwanted Website</t>
+          <t>Online productivity web tool featured in TrickPilot: Save this if you play Games</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>Remove Your Gmail Id From Unwanted Website</t>
+          <t>Save this if you play Games</t>
         </is>
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/9QD7cxwr3Yk</t>
+          <t>https://www.youtube.com/shorts/gyyA2CjXXDc</t>
         </is>
       </c>
     </row>
     <row r="131" ht="22" customHeight="1">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>Safety Tips</t>
+          <t>Save your time in future</t>
         </is>
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Safety+Tips</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Safety Tips</t>
+          <t>Online productivity web tool featured in TrickPilot: Save Your Time in Future</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr">
         <is>
-          <t>Safety Tips</t>
+          <t>Save Your Time in Future</t>
         </is>
       </c>
       <c r="F131" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/CozH9RSszMk</t>
+          <t>https://www.youtube.com/shorts/Fu2QEqEw69c</t>
         </is>
       </c>
     </row>
     <row r="132" ht="22" customHeight="1">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Samajh nhi aa rha caption kya dalu</t>
+          <t>Save your time with this extension</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Samajh+nhi+aa+rha+caption+kya+dalu</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Samajh nhi aa rha caption kya dalu</t>
+          <t>Online productivity web tool featured in TrickPilot: Save Your Time With This Extension</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>Samajh nhi aa rha caption kya dalu</t>
+          <t>Save Your Time With This Extension</t>
         </is>
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/sXubpOO59I4</t>
+          <t>https://www.youtube.com/shorts/HOya-cmvxU4</t>
         </is>
       </c>
     </row>
     <row r="133" ht="22" customHeight="1">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>Save Your Time With This Extension</t>
+          <t>Searching for a job ? try this</t>
         </is>
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Save+Your+Time+With+This+Extension</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Save Your Time With This Extension</t>
+          <t>Online productivity web tool featured in TrickPilot: Searching For A Job ? Try this</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>Save Your Time With This Extension</t>
+          <t>Searching For A Job ? Try this</t>
         </is>
       </c>
       <c r="F133" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/HOya-cmvxU4</t>
+          <t>https://www.youtube.com/shorts/KHmVkjcmFak</t>
         </is>
       </c>
     </row>
     <row r="134" ht="22" customHeight="1">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Save Your Time in Future</t>
+          <t>Secret website</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Save+Your+Time+in+Future</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Save Your Time in Future</t>
+          <t>Online productivity web tool featured in TrickPilot: secret website</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>Save Your Time in Future</t>
+          <t>secret website</t>
         </is>
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/Fu2QEqEw69c</t>
+          <t>https://www.youtube.com/shorts/C9dIEFY7h7M</t>
         </is>
       </c>
     </row>
     <row r="135" ht="22" customHeight="1">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>Save these hacks for your PC</t>
+          <t>Secret websites</t>
         </is>
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Save+these+hacks+for+your+PC</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Save these hacks for your PC</t>
+          <t>Online productivity web tool featured in TrickPilot: Secret Websites</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr">
         <is>
-          <t>Save these hacks for your PC</t>
+          <t>Secret Websites</t>
         </is>
       </c>
       <c r="F135" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/UkxHlxE5ZFI</t>
+          <t>https://www.youtube.com/shorts/IyxbDhUmWQc</t>
         </is>
       </c>
     </row>
     <row r="136" ht="22" customHeight="1">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Save this 4-step formula</t>
+          <t>Secrets of meme pages</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Save+this+4step+formula</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Save this 4-step formula</t>
+          <t>Online productivity web tool featured in TrickPilot: Secrets of meme pages</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>Save this 4-step formula</t>
+          <t>Secrets of meme pages</t>
         </is>
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>CHAT GPT</t>
+          <t>https://www.youtube.com/shorts/2NXeNIlZIzE</t>
         </is>
       </c>
     </row>
     <row r="137" ht="22" customHeight="1">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>Save this for Kids</t>
+          <t>Secure your family and get high returns</t>
         </is>
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Save+this+for+Kids</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Save this for Kids</t>
+          <t>Online productivity web tool featured in TrickPilot: Secure Your Family And Get High Returns</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
-          <t>Save this for Kids</t>
+          <t>Secure Your Family And Get High Returns</t>
         </is>
       </c>
       <c r="F137" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/zFyDgq1nMgw</t>
+          <t>https://www.youtube.com/shorts/G7QkQMN81eI</t>
         </is>
       </c>
     </row>
     <row r="138" ht="22" customHeight="1">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Save this if you play Games</t>
+          <t>See if you are noob or pro</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Save+this+if+you+play+Games</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Save this if you play Games</t>
+          <t>Online productivity web tool featured in TrickPilot: See if you are Noob or Pro</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>Save this if you play Games</t>
+          <t>See if you are Noob or Pro</t>
         </is>
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/gyyA2CjXXDc</t>
+          <t>https://www.youtube.com/shorts/CLT5kDedBz8</t>
         </is>
       </c>
     </row>
     <row r="139" ht="22" customHeight="1">
       <c r="A139" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>Searching For A Job ? Try this</t>
+          <t>Self control cat control</t>
         </is>
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Searching+For+A+Job++Try+this</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Searching For A Job ? Try this</t>
+          <t>Online productivity web tool featured in TrickPilot: Self Control Cat Control</t>
         </is>
       </c>
       <c r="E139" s="4" t="inlineStr">
         <is>
-          <t>Searching For A Job ? Try this</t>
+          <t>Self Control Cat Control</t>
         </is>
       </c>
       <c r="F139" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/KHmVkjcmFak</t>
+          <t>https://www.youtube.com/shorts/-UjtTaM9WAM</t>
         </is>
       </c>
     </row>
     <row r="140" ht="22" customHeight="1">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Secret Websites</t>
+          <t>Share with friends and family</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Secret+Websites</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Secret Websites</t>
+          <t>Online productivity web tool featured in TrickPilot: Share With Friends and Family</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>Secret Websites</t>
+          <t>Share With Friends and Family</t>
         </is>
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/IyxbDhUmWQc</t>
+          <t>https://www.youtube.com/shorts/AFABCup4Oc0</t>
         </is>
       </c>
     </row>
     <row r="141" ht="22" customHeight="1">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>Secrets of meme pages</t>
+          <t>Slide deck feature is really impressive</t>
         </is>
       </c>
       <c r="C141" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Secrets+of+meme+pages</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Secrets of meme pages</t>
+          <t>Online productivity web tool featured in TrickPilot: Slide deck feature is really impressive</t>
         </is>
       </c>
       <c r="E141" s="4" t="inlineStr">
         <is>
-          <t>Secrets of meme pages</t>
+          <t>Slide deck feature is really impressive</t>
         </is>
       </c>
       <c r="F141" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/2NXeNIlZIzE</t>
+          <t>https://www.youtube.com/shorts/qmh9aR53i4U</t>
         </is>
       </c>
     </row>
     <row r="142" ht="22" customHeight="1">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Secure Your Family And Get High Returns</t>
+          <t>Snapchat be like: memories aint fre</t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Secure+Your+Family+And+Get+High+Returns</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Secure Your Family And Get High Returns</t>
+          <t>Online productivity web tool featured in TrickPilot: Snapchat be like: memories aint free, buddy</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>Secure Your Family And Get High Returns</t>
+          <t>Snapchat be like: memories aint free, buddy</t>
         </is>
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/G7QkQMN81eI</t>
+          <t>https://www.youtube.com/shorts/1Mq9e3KfCRA</t>
         </is>
       </c>
     </row>
     <row r="143" ht="22" customHeight="1">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>See if you are Noob or Pro</t>
+          <t>Start learning generative ai</t>
         </is>
       </c>
       <c r="C143" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=See+if+you+are+Noob+or+Pro</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: See if you are Noob or Pro</t>
+          <t>Online productivity web tool featured in TrickPilot: Start learning Generative AI</t>
         </is>
       </c>
       <c r="E143" s="4" t="inlineStr">
         <is>
-          <t>See if you are Noob or Pro</t>
+          <t>Start learning Generative AI</t>
         </is>
       </c>
       <c r="F143" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/CLT5kDedBz8</t>
+          <t>https://www.youtube.com/shorts/IoslCQQ4lcE</t>
         </is>
       </c>
     </row>
     <row r="144" ht="22" customHeight="1">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Self Control Cat Control</t>
+          <t>Super useful extension</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Self+Control+Cat+Control</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Self Control Cat Control</t>
+          <t>Online productivity web tool featured in TrickPilot: Super Useful Extension</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>Self Control Cat Control</t>
+          <t>Super Useful Extension</t>
         </is>
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/-UjtTaM9WAM</t>
+          <t>https://www.youtube.com/shorts/VHNWGw7LzUY</t>
         </is>
       </c>
     </row>
     <row r="145" ht="22" customHeight="1">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>Share With Friends and Family</t>
+          <t>Take your test with gemini</t>
         </is>
       </c>
       <c r="C145" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Share+With+Friends+and+Family</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Share With Friends and Family</t>
+          <t>Online productivity web tool featured in TrickPilot: Take your test with Gemini</t>
         </is>
       </c>
       <c r="E145" s="4" t="inlineStr">
         <is>
-          <t>Share With Friends and Family</t>
+          <t>Take your test with Gemini</t>
         </is>
       </c>
       <c r="F145" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/AFABCup4Oc0</t>
+          <t>https://www.youtube.com/shorts/F8ABSl5EOuQ</t>
         </is>
       </c>
     </row>
     <row r="146" ht="22" customHeight="1">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Should be Afraid of or be Happy ?</t>
+          <t>These websites are weird / intresting</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Should+be+Afraid+of+or+be+Happy</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Should be Afraid of or be Happy ?</t>
+          <t>Online productivity web tool featured in TrickPilot: These websites are Weird / Intresting</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>Should be Afraid of or be Happy ?</t>
+          <t>These websites are Weird / Intresting</t>
         </is>
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/McHYFVZMwQ0</t>
+          <t>https://www.youtube.com/shorts/cDCwlP5DnKg</t>
         </is>
       </c>
     </row>
     <row r="147" ht="22" customHeight="1">
       <c r="A147" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>Slide deck feature is really impressive</t>
+          <t>This is crazy</t>
         </is>
       </c>
       <c r="C147" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Slide+deck+feature+is+really+impressive</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Slide deck feature is really impressive</t>
+          <t>Online productivity web tool featured in TrickPilot: This is Crazy</t>
         </is>
       </c>
       <c r="E147" s="4" t="inlineStr">
         <is>
-          <t>Slide deck feature is really impressive</t>
+          <t>This is Crazy</t>
         </is>
       </c>
       <c r="F147" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/qmh9aR53i4U</t>
+          <t>https://www.youtube.com/shorts/ME86NBrMwB8</t>
         </is>
       </c>
     </row>
     <row r="148" ht="22" customHeight="1">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Snapchat be like: memories aint free, buddy</t>
+          <t>This is so cool</t>
         </is>
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Snapchat+be+like+memories+aint+free+buddy</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Snapchat be like: memories aint free, buddy</t>
+          <t>Online productivity web tool featured in TrickPilot: This is so cool</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>Snapchat be like: memories aint free, buddy</t>
+          <t>This is so cool</t>
         </is>
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/1Mq9e3KfCRA</t>
+          <t>https://www.youtube.com/shorts/3heGPWwee3E</t>
         </is>
       </c>
     </row>
     <row r="149" ht="22" customHeight="1">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>Start learning Generative AI</t>
+          <t>This new technology is crazy</t>
         </is>
       </c>
       <c r="C149" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Start+learning+Generative+AI</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Start learning Generative AI</t>
+          <t>Online productivity web tool featured in TrickPilot: This new technology is Crazy</t>
         </is>
       </c>
       <c r="E149" s="4" t="inlineStr">
         <is>
-          <t>Start learning Generative AI</t>
+          <t>This new technology is Crazy</t>
         </is>
       </c>
       <c r="F149" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/IoslCQQ4lcE</t>
+          <t>https://www.youtube.com/shorts/xZQ6u1sIvXc</t>
         </is>
       </c>
     </row>
     <row r="150" ht="22" customHeight="1">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Students Save this video</t>
+          <t>This number can block any website</t>
         </is>
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Students+Save+this+video</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Students Save this video</t>
+          <t>Online productivity web tool featured in TrickPilot: This Number Can Block Any Website</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>Students Save this video</t>
+          <t>This Number Can Block Any Website</t>
         </is>
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/27vZ-IjaCZQ</t>
+          <t>https://www.youtube.com/shorts/pNXLtw-R6a4</t>
         </is>
       </c>
     </row>
     <row r="151" ht="22" customHeight="1">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>Super Useful Extension</t>
+          <t>This pc is worth a fortuner</t>
         </is>
       </c>
       <c r="C151" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Super+Useful+Extension</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Super Useful Extension</t>
+          <t>Online productivity web tool featured in TrickPilot: This PC is worth a Fortuner</t>
         </is>
       </c>
       <c r="E151" s="4" t="inlineStr">
         <is>
-          <t>Super Useful Extension</t>
+          <t>This PC is worth a Fortuner</t>
         </is>
       </c>
       <c r="F151" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/VHNWGw7LzUY</t>
+          <t>https://www.youtube.com/shorts/S2DQWmAZQa4</t>
         </is>
       </c>
     </row>
     <row r="152" ht="22" customHeight="1">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Take your test with Gemini</t>
+          <t>This software is game changer</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Take+your+test+with+Gemini</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Take your test with Gemini</t>
+          <t>Online productivity web tool featured in TrickPilot: This software is game changer</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>Take your test with Gemini</t>
+          <t>This software is game changer</t>
         </is>
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/F8ABSl5EOuQ</t>
+          <t>https://www.youtube.com/shorts/VwO_UPhHrIY</t>
         </is>
       </c>
     </row>
     <row r="153" ht="22" customHeight="1">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>These websites are Weird / Intresting</t>
+          <t>This tool is crazy</t>
         </is>
       </c>
       <c r="C153" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=These+websites+are+Weird++Intresting</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: These websites are Weird / Intresting</t>
+          <t>Online productivity web tool featured in TrickPilot: This Tool Is Crazy</t>
         </is>
       </c>
       <c r="E153" s="4" t="inlineStr">
         <is>
-          <t>These websites are Weird / Intresting</t>
+          <t>This Tool Is Crazy</t>
         </is>
       </c>
       <c r="F153" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/cDCwlP5DnKg</t>
+          <t>https://www.youtube.com/shorts/61Ri2M3Rmpw</t>
         </is>
       </c>
     </row>
     <row r="154" ht="22" customHeight="1">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>This Number Can Block Any Website</t>
+          <t>This tool will make your videos viral</t>
         </is>
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=This+Number+Can+Block+Any+Website</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: This Number Can Block Any Website</t>
+          <t>Online productivity web tool featured in TrickPilot: This tool will make your videos Viral</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>This Number Can Block Any Website</t>
+          <t>This tool will make your videos Viral</t>
         </is>
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/pNXLtw-R6a4</t>
+          <t>https://www.youtube.com/shorts/iKvildDqvMA</t>
         </is>
       </c>
     </row>
     <row r="155" ht="22" customHeight="1">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>This PC is worth a Fortuner</t>
+          <t>This website is insane</t>
         </is>
       </c>
       <c r="C155" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=This+PC+is+worth+a+Fortuner</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: This PC is worth a Fortuner</t>
+          <t>Online productivity web tool featured in TrickPilot: This Website Is Insane</t>
         </is>
       </c>
       <c r="E155" s="4" t="inlineStr">
         <is>
-          <t>This PC is worth a Fortuner</t>
+          <t>This Website Is Insane</t>
         </is>
       </c>
       <c r="F155" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/S2DQWmAZQa4</t>
+          <t>https://www.youtube.com/shorts/AJWLQbEYpJo</t>
         </is>
       </c>
     </row>
     <row r="156" ht="22" customHeight="1">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>This Tool Is Crazy</t>
+          <t>This website will make life easy</t>
         </is>
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=This+Tool+Is+Crazy</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: This Tool Is Crazy</t>
+          <t>Online productivity web tool featured in TrickPilot: This Website will make life easy</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>This Tool Is Crazy</t>
+          <t>This Website will make life easy</t>
         </is>
       </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/61Ri2M3Rmpw</t>
+          <t>https://www.youtube.com/shorts/75VJUx_aPtc</t>
         </is>
       </c>
     </row>
     <row r="157" ht="22" customHeight="1">
       <c r="A157" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>This Website Is Insane</t>
+          <t xml:space="preserve">This will definitely bring a smile </t>
         </is>
       </c>
       <c r="C157" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=This+Website+Is+Insane</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: This Website Is Insane</t>
+          <t>Online productivity web tool featured in TrickPilot: This will definitely bring a smile to your face</t>
         </is>
       </c>
       <c r="E157" s="4" t="inlineStr">
         <is>
-          <t>This Website Is Insane</t>
+          <t>This will definitely bring a smile to your face</t>
         </is>
       </c>
       <c r="F157" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/AJWLQbEYpJo</t>
+          <t>https://www.youtube.com/shorts/mZg5b9lh7-k</t>
         </is>
       </c>
     </row>
     <row r="158" ht="22" customHeight="1">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>This Website will make life easy</t>
+          <t>This will make your life easy</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=This+Website+will+make+life+easy</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: This Website will make life easy</t>
+          <t>Online productivity web tool featured in TrickPilot: This Will Make Your Life Easy</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>This Website will make life easy</t>
+          <t>This Will Make Your Life Easy</t>
         </is>
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/75VJUx_aPtc</t>
+          <t>https://www.youtube.com/shorts/v0q5_87aXJg</t>
         </is>
       </c>
     </row>
     <row r="159" ht="22" customHeight="1">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>This Will Make Your Life Easy</t>
+          <t>Transform your pc</t>
         </is>
       </c>
       <c r="C159" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=This+Will+Make+Your+Life+Easy</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: This Will Make Your Life Easy</t>
+          <t>Online productivity web tool featured in TrickPilot: Transform your PC</t>
         </is>
       </c>
       <c r="E159" s="4" t="inlineStr">
         <is>
-          <t>This Will Make Your Life Easy</t>
+          <t>Transform your PC</t>
         </is>
       </c>
       <c r="F159" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/v0q5_87aXJg</t>
+          <t>https://www.youtube.com/shorts/ofVmHcKn3ig</t>
         </is>
       </c>
     </row>
     <row r="160" ht="22" customHeight="1">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>This is Crazy</t>
+          <t>Transform your pc cursor</t>
         </is>
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=This+is+Crazy</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: This is Crazy</t>
+          <t>Online productivity web tool featured in TrickPilot: Transform your PC Cursor</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>This is Crazy</t>
+          <t>Transform your PC Cursor</t>
         </is>
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/ME86NBrMwB8</t>
+          <t>https://www.youtube.com/shorts/tDEFoBjrYnM</t>
         </is>
       </c>
     </row>
     <row r="161" ht="22" customHeight="1">
       <c r="A161" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>This is so cool</t>
+          <t>Transformer your normal pic into pr</t>
         </is>
       </c>
       <c r="C161" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=This+is+so+cool</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: This is so cool</t>
+          <t>Online productivity web tool featured in TrickPilot: Transformer Your Normal Pic Into Professional</t>
         </is>
       </c>
       <c r="E161" s="4" t="inlineStr">
         <is>
-          <t>This is so cool</t>
+          <t>Transformer Your Normal Pic Into Professional</t>
         </is>
       </c>
       <c r="F161" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/3heGPWwee3E</t>
+          <t>https://www.youtube.com/shorts/k9TRBwqXY58</t>
         </is>
       </c>
     </row>
     <row r="162" ht="22" customHeight="1">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>This new technology is Crazy</t>
+          <t>Trick to improve wifi speed</t>
         </is>
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=This+new+technology+is+Crazy</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: This new technology is Crazy</t>
+          <t>Online productivity web tool featured in TrickPilot: Trick to improve WiFi Speed</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>This new technology is Crazy</t>
+          <t>Trick to improve WiFi Speed</t>
         </is>
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/xZQ6u1sIvXc</t>
+          <t>https://www.youtube.com/shorts/UINJzV27X0E</t>
         </is>
       </c>
     </row>
     <row r="163" ht="22" customHeight="1">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>This software is game changer</t>
+          <t>Try these website when you feel bored</t>
         </is>
       </c>
       <c r="C163" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=This+software+is+game+changer</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: This software is game changer</t>
+          <t>Online productivity web tool featured in TrickPilot: Try These Website When You Feel Bored</t>
         </is>
       </c>
       <c r="E163" s="4" t="inlineStr">
         <is>
-          <t>This software is game changer</t>
+          <t>Try These Website When You Feel Bored</t>
         </is>
       </c>
       <c r="F163" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/VwO_UPhHrIY</t>
+          <t>https://www.youtube.com/shorts/S_PHAjDHKHY</t>
         </is>
       </c>
     </row>
     <row r="164" ht="22" customHeight="1">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>This tool will make your videos Viral</t>
+          <t>Try this animated story</t>
         </is>
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=This+tool+will+make+your+videos+Viral</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: This tool will make your videos Viral</t>
+          <t>Online productivity web tool featured in TrickPilot: Try this animated story</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>This tool will make your videos Viral</t>
+          <t>Try this animated story</t>
         </is>
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/iKvildDqvMA</t>
+          <t>https://www.youtube.com/shorts/1Oxv5NmWUDo</t>
         </is>
       </c>
     </row>
     <row r="165" ht="22" customHeight="1">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>This will definitely bring a smile to your fa</t>
+          <t>Try this with your pc</t>
         </is>
       </c>
       <c r="C165" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=This+will+definitely+bring+a+smile+to+your+face</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: This will definitely bring a smile to your face</t>
+          <t>Online productivity web tool featured in TrickPilot: Try this with your PC</t>
         </is>
       </c>
       <c r="E165" s="4" t="inlineStr">
         <is>
-          <t>This will definitely bring a smile to your face</t>
+          <t>Try this with your PC</t>
         </is>
       </c>
       <c r="F165" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/mZg5b9lh7-k</t>
+          <t>https://www.youtube.com/shorts/W9oFB9jjpbY</t>
         </is>
       </c>
     </row>
     <row r="166" ht="22" customHeight="1">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>Transform your PC</t>
+          <t>Turn your dusty old laptop into a l</t>
         </is>
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Transform+your+PC</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Transform your PC</t>
+          <t>Online productivity web tool featured in TrickPilot: Turn your dusty old laptop into a lightning-fast Chromebook</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>Transform your PC</t>
+          <t>Turn your dusty old laptop into a lightning-fast Chromebook</t>
         </is>
       </c>
       <c r="F166" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/ofVmHcKn3ig</t>
+          <t>https://www.youtube.com/shorts/qYJXe7tWKhE</t>
         </is>
       </c>
     </row>
     <row r="167" ht="22" customHeight="1">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>Transform your PC Cursor</t>
+          <t>TypeRacer</t>
         </is>
       </c>
       <c r="C167" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Transform+your+PC+Cursor</t>
+          <t>https://play.typeracer.com</t>
         </is>
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Transform your PC Cursor</t>
+          <t>Multiplayer online typing competition game to test and improve words-per-minute speed.</t>
         </is>
       </c>
       <c r="E167" s="4" t="inlineStr">
         <is>
-          <t>Transform your PC Cursor</t>
+          <t>Wishlist this typing game</t>
         </is>
       </c>
       <c r="F167" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/tDEFoBjrYnM</t>
+          <t>https://www.youtube.com/shorts/m6LBfv7E1BU</t>
         </is>
       </c>
     </row>
     <row r="168" ht="22" customHeight="1">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>Transformer Your Normal Pic Into Professional</t>
+          <t xml:space="preserve">Uninstall permanently any software </t>
         </is>
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Transformer+Your+Normal+Pic+Into+Professional</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Transformer Your Normal Pic Into Professional</t>
+          <t>Online productivity web tool featured in TrickPilot: Uninstall permanently Any software on your pc</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>Transformer Your Normal Pic Into Professional</t>
+          <t>Uninstall permanently Any software on your pc</t>
         </is>
       </c>
       <c r="F168" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/k9TRBwqXY58</t>
+          <t>https://www.youtube.com/shorts/uRsu6Hkzo1k</t>
         </is>
       </c>
     </row>
     <row r="169" ht="22" customHeight="1">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>Trick to improve WiFi Speed</t>
+          <t>Use google smartly</t>
         </is>
       </c>
       <c r="C169" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Trick+to+improve+WiFi+Speed</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Trick to improve WiFi Speed</t>
+          <t>Online productivity web tool featured in TrickPilot: Use Google Smartly</t>
         </is>
       </c>
       <c r="E169" s="4" t="inlineStr">
         <is>
-          <t>Trick to improve WiFi Speed</t>
+          <t>Use Google Smartly</t>
         </is>
       </c>
       <c r="F169" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/UINJzV27X0E</t>
+          <t>https://www.youtube.com/shorts/dxijnB-C0b0</t>
         </is>
       </c>
     </row>
     <row r="170" ht="22" customHeight="1">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>Try this animated story</t>
+          <t>Use in moderation</t>
         </is>
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Try+this+animated+story</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Try this animated story</t>
+          <t>Online productivity web tool featured in TrickPilot: Use in Moderation</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>Try this animated story</t>
+          <t>Use in Moderation</t>
         </is>
       </c>
       <c r="F170" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/1Oxv5NmWUDo</t>
+          <t>https://www.youtube.com/shorts/zidP16xbFfI</t>
         </is>
       </c>
     </row>
     <row r="171" ht="22" customHeight="1">
       <c r="A171" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>Try this with your PC</t>
+          <t>Use readdy ai to build websites</t>
         </is>
       </c>
       <c r="C171" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Try+this+with+your+PC</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Try this with your PC</t>
+          <t>Online productivity web tool featured in TrickPilot: Use Readdy AI to build websites</t>
         </is>
       </c>
       <c r="E171" s="4" t="inlineStr">
         <is>
-          <t>Try this with your PC</t>
+          <t>Use Readdy AI to build websites</t>
         </is>
       </c>
       <c r="F171" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/W9oFB9jjpbY</t>
+          <t>https://www.youtube.com/shorts/89O4PqnGagA</t>
         </is>
       </c>
     </row>
     <row r="172" ht="22" customHeight="1">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>Turn Idea into apps - Instantly</t>
+          <t>Use this to make emails professional</t>
         </is>
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Turn+Idea+into+apps++Instantly</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Turn Idea into apps - Instantly</t>
+          <t>Online productivity web tool featured in TrickPilot: Use This To Make Emails Professional</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>Turn Idea into apps - Instantly</t>
+          <t>Use This To Make Emails Professional</t>
         </is>
       </c>
       <c r="F172" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/b86HZqtXRVo</t>
+          <t>https://www.youtube.com/shorts/Ykj8ZhaJJz8</t>
         </is>
       </c>
     </row>
     <row r="173" ht="22" customHeight="1">
       <c r="A173" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>Turn your Phone Into CCTV</t>
+          <t>Use your phone as a mouse/keyboard</t>
         </is>
       </c>
       <c r="C173" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Turn+your+Phone+Into+CCTV</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Turn your Phone Into CCTV</t>
+          <t>Online productivity web tool featured in TrickPilot: Use Your Phone As A Mouse/Keyboard</t>
         </is>
       </c>
       <c r="E173" s="4" t="inlineStr">
         <is>
-          <t>Turn your Phone Into CCTV</t>
+          <t>Use Your Phone As A Mouse/Keyboard</t>
         </is>
       </c>
       <c r="F173" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/KpXYsI8lZ0Y</t>
+          <t>https://www.youtube.com/shorts/0NB4AoG_IM0</t>
         </is>
       </c>
     </row>
     <row r="174" ht="22" customHeight="1">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>Turn your dusty old laptop into a lightning-f</t>
+          <t>Useful software for your pc</t>
         </is>
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Turn+your+dusty+old+laptop+into+a+lightningfast+Chromebook</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Turn your dusty old laptop into a lightning-fast Chromebook</t>
+          <t>Online productivity web tool featured in TrickPilot: Useful Software for your PC</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>Turn your dusty old laptop into a lightning-fast Chromebook</t>
+          <t>Useful Software for your PC</t>
         </is>
       </c>
       <c r="F174" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/qYJXe7tWKhE</t>
+          <t>https://www.youtube.com/shorts/zBFGnMVuMbE</t>
         </is>
       </c>
     </row>
     <row r="175" ht="22" customHeight="1">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>Turn your keyboard into mechanical</t>
+          <t>Uttar pradesh rising numbers dont lie.</t>
         </is>
       </c>
       <c r="C175" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Turn+your+keyboard+into+mechanical</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Turn your keyboard into mechanical</t>
+          <t>Online productivity web tool featured in TrickPilot: Uttar Pradesh rising numbers dont lie.</t>
         </is>
       </c>
       <c r="E175" s="4" t="inlineStr">
         <is>
-          <t>Turn your keyboard into mechanical</t>
+          <t>Uttar Pradesh rising numbers dont lie.</t>
         </is>
       </c>
       <c r="F175" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/xzjmY8z1xJw</t>
+          <t>https://www.youtube.com/shorts/K_mFwkt73Ik</t>
         </is>
       </c>
     </row>
     <row r="176" ht="22" customHeight="1">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>Uninstall permanently Any software on your pc</t>
+          <t>Very easy way to sign documents</t>
         </is>
       </c>
       <c r="C176" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Uninstall+permanently+Any+software+on+your+pc</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Uninstall permanently Any software on your pc</t>
+          <t>Online productivity web tool featured in TrickPilot: Very Easy Way To Sign Documents</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>Uninstall permanently Any software on your pc</t>
+          <t>Very Easy Way To Sign Documents</t>
         </is>
       </c>
       <c r="F176" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/uRsu6Hkzo1k</t>
+          <t>https://www.youtube.com/shorts/5aVyajhAulI</t>
         </is>
       </c>
     </row>
     <row r="177" ht="22" customHeight="1">
       <c r="A177" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>Use Google Smartly</t>
+          <t>Visualise your dream house</t>
         </is>
       </c>
       <c r="C177" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Use+Google+Smartly</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Use Google Smartly</t>
+          <t>Online productivity web tool featured in TrickPilot: Visualise your dream house</t>
         </is>
       </c>
       <c r="E177" s="4" t="inlineStr">
         <is>
-          <t>Use Google Smartly</t>
+          <t>Visualise your dream house</t>
         </is>
       </c>
       <c r="F177" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/dxijnB-C0b0</t>
+          <t>https://www.youtube.com/shorts/L_METrimCDo</t>
         </is>
       </c>
     </row>
     <row r="178" ht="22" customHeight="1">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>Use Readdy AI to build websites</t>
+          <t>Want to learn high paying skills</t>
         </is>
       </c>
       <c r="C178" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Use+Readdy+AI+to+build+websites</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Use Readdy AI to build websites</t>
+          <t>Online productivity web tool featured in TrickPilot: Want To Learn High Paying Skills</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>Use Readdy AI to build websites</t>
+          <t>Want To Learn High Paying Skills</t>
         </is>
       </c>
       <c r="F178" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/89O4PqnGagA</t>
+          <t>https://www.youtube.com/shorts/nD2HzvXDB6c</t>
         </is>
       </c>
     </row>
     <row r="179" ht="22" customHeight="1">
       <c r="A179" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>Use This To Make Emails Professional</t>
+          <t>Watch this before buying laptop</t>
         </is>
       </c>
       <c r="C179" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Use+This+To+Make+Emails+Professional</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Use This To Make Emails Professional</t>
+          <t>Online productivity web tool featured in TrickPilot: Watch this before buying laptop</t>
         </is>
       </c>
       <c r="E179" s="4" t="inlineStr">
         <is>
-          <t>Use This To Make Emails Professional</t>
+          <t>Watch this before buying laptop</t>
         </is>
       </c>
       <c r="F179" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/Ykj8ZhaJJz8</t>
+          <t>https://www.youtube.com/shorts/-zLSi0RVCrU</t>
         </is>
       </c>
     </row>
     <row r="180" ht="22" customHeight="1">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>Use Your Phone As A Mouse/Keyboard</t>
+          <t>Website in just 5 minutes</t>
         </is>
       </c>
       <c r="C180" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Use+Your+Phone+As+A+MouseKeyboard</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Use Your Phone As A Mouse/Keyboard</t>
+          <t>Online productivity web tool featured in TrickPilot: Create Website In Just 5 Minutes</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>Use Your Phone As A Mouse/Keyboard</t>
+          <t>Create Website In Just 5 Minutes</t>
         </is>
       </c>
       <c r="F180" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/0NB4AoG_IM0</t>
+          <t>https://www.youtube.com/shorts/-6CjzhPtJ24</t>
         </is>
       </c>
     </row>
     <row r="181" ht="22" customHeight="1">
       <c r="A181" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>Use in Moderation</t>
+          <t>Websites for minecraft folks</t>
         </is>
       </c>
       <c r="C181" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Use+in+Moderation</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Use in Moderation</t>
+          <t>Online productivity web tool featured in TrickPilot: Websites for Minecraft folks</t>
         </is>
       </c>
       <c r="E181" s="4" t="inlineStr">
         <is>
-          <t>Use in Moderation</t>
+          <t>Websites for Minecraft folks</t>
         </is>
       </c>
       <c r="F181" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/zidP16xbFfI</t>
+          <t>https://www.youtube.com/shorts/N2DkE_L-lo4</t>
         </is>
       </c>
     </row>
     <row r="182" ht="22" customHeight="1">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>Use this cool Application</t>
+          <t>What do you think about this ?</t>
         </is>
       </c>
       <c r="C182" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Use+this+cool+Application</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Use this cool Application</t>
+          <t>Online productivity web tool featured in TrickPilot: What do you think about this ?</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>Use this cool Application</t>
+          <t>What do you think about this ?</t>
         </is>
       </c>
       <c r="F182" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/F1e0009-XCk</t>
+          <t>https://www.youtube.com/shorts/UKm6Ry9nTZQ</t>
         </is>
       </c>
     </row>
     <row r="183" ht="22" customHeight="1">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>Useful Software for your PC</t>
+          <t>Who made this weird game</t>
         </is>
       </c>
       <c r="C183" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Useful+Software+for+your+PC</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D183" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Useful Software for your PC</t>
+          <t>Online productivity web tool featured in TrickPilot: Who made this Weird Game</t>
         </is>
       </c>
       <c r="E183" s="4" t="inlineStr">
         <is>
-          <t>Useful Software for your PC</t>
+          <t>Who made this Weird Game</t>
         </is>
       </c>
       <c r="F183" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/zBFGnMVuMbE</t>
+          <t>https://www.youtube.com/shorts/f0hib5WtXIU</t>
         </is>
       </c>
     </row>
     <row r="184" ht="22" customHeight="1">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>Uttar Pradesh rising numbers dont lie.</t>
+          <t>Why struggle when you can learn smarter?</t>
         </is>
       </c>
       <c r="C184" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Uttar+Pradesh+rising+numbers+dont+lie</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Uttar Pradesh rising numbers dont lie.</t>
+          <t>Online productivity web tool featured in TrickPilot: Why struggle when you can learn smarter?</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>Uttar Pradesh rising numbers dont lie.</t>
+          <t>Why struggle when you can learn smarter?</t>
         </is>
       </c>
       <c r="F184" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/K_mFwkt73Ik</t>
+          <t>https://www.youtube.com/shorts/KLEFeEXkzu4</t>
         </is>
       </c>
     </row>
     <row r="185" ht="22" customHeight="1">
       <c r="A185" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>Very Easy Way To Sign Documents</t>
+          <t>Windows telemetry</t>
         </is>
       </c>
       <c r="C185" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Very+Easy+Way+To+Sign+Documents</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D185" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Very Easy Way To Sign Documents</t>
+          <t>Online productivity web tool featured in TrickPilot: Windows Telemetry</t>
         </is>
       </c>
       <c r="E185" s="4" t="inlineStr">
         <is>
-          <t>Very Easy Way To Sign Documents</t>
+          <t>Windows Telemetry</t>
         </is>
       </c>
       <c r="F185" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/5aVyajhAulI</t>
+          <t>https://www.youtube.com/shorts/Bq0p3o3taZ0</t>
         </is>
       </c>
     </row>
     <row r="186" ht="22" customHeight="1">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>Visualise your dream house</t>
+          <t>Wish birthday like this</t>
         </is>
       </c>
       <c r="C186" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Visualise+your+dream+house</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Visualise your dream house</t>
+          <t>Online productivity web tool featured in TrickPilot: Wish Birthday like this</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>Visualise your dream house</t>
+          <t>Wish Birthday like this</t>
         </is>
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/L_METrimCDo</t>
+          <t>https://www.youtube.com/shorts/VQ6pgCCoNcQ</t>
         </is>
       </c>
     </row>
     <row r="187" ht="22" customHeight="1">
       <c r="A187" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>Want To Learn High Paying Skills</t>
+          <t>World tour with 0 money</t>
         </is>
       </c>
       <c r="C187" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Want+To+Learn+High+Paying+Skills</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D187" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Want To Learn High Paying Skills</t>
+          <t>Online productivity web tool featured in TrickPilot: World tour with 0 money</t>
         </is>
       </c>
       <c r="E187" s="4" t="inlineStr">
         <is>
-          <t>Want To Learn High Paying Skills</t>
+          <t>World tour with 0 money</t>
         </is>
       </c>
       <c r="F187" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/nD2HzvXDB6c</t>
+          <t>https://www.youtube.com/shorts/uXrgTC1cEws</t>
         </is>
       </c>
     </row>
     <row r="188" ht="22" customHeight="1">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>Websites for Minecraft folks</t>
+          <t>You dont need antivirus</t>
         </is>
       </c>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Websites+for+Minecraft+folks</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Websites for Minecraft folks</t>
+          <t>Online productivity web tool featured in TrickPilot: You Dont Need Antivirus</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>Websites for Minecraft folks</t>
+          <t>You Dont Need Antivirus</t>
         </is>
       </c>
       <c r="F188" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/N2DkE_L-lo4</t>
+          <t>https://www.youtube.com/shorts/g-bRucHk7OE</t>
         </is>
       </c>
     </row>
     <row r="189" ht="22" customHeight="1">
       <c r="A189" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>What do you think about this ?</t>
+          <t>Your dream pc in seconds</t>
         </is>
       </c>
       <c r="C189" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=What+do+you+think+about+this</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D189" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: What do you think about this ?</t>
+          <t>Online productivity web tool featured in TrickPilot: Build your dream PC in seconds</t>
         </is>
       </c>
       <c r="E189" s="4" t="inlineStr">
         <is>
-          <t>What do you think about this ?</t>
+          <t>Build your dream PC in seconds</t>
         </is>
       </c>
       <c r="F189" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/UKm6Ry9nTZQ</t>
+          <t>https://www.youtube.com/shorts/vS9zbNL0gj0</t>
         </is>
       </c>
     </row>
     <row r="190" ht="22" customHeight="1">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>WhatsApp New Feature</t>
+          <t>Your keyboard into mechanical</t>
         </is>
       </c>
       <c r="C190" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=WhatsApp+New+Feature</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: WhatsApp New Feature</t>
+          <t>Online productivity web tool featured in TrickPilot: Turn your keyboard into mechanical</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>WhatsApp New Feature</t>
+          <t>Turn your keyboard into mechanical</t>
         </is>
       </c>
       <c r="F190" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/tr686LQDlBQ</t>
+          <t>https://www.youtube.com/shorts/xzjmY8z1xJw</t>
         </is>
       </c>
     </row>
     <row r="191" ht="22" customHeight="1">
       <c r="A191" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>Who made this Weird Game</t>
+          <t>Your pc is always in hibernation</t>
         </is>
       </c>
       <c r="C191" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Who+made+this+Weird+Game</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D191" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Who made this Weird Game</t>
+          <t>Online productivity web tool featured in TrickPilot: Your Pc is always in hibernation</t>
         </is>
       </c>
       <c r="E191" s="4" t="inlineStr">
         <is>
-          <t>Who made this Weird Game</t>
+          <t>Your Pc is always in hibernation</t>
         </is>
       </c>
       <c r="F191" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/f0hib5WtXIU</t>
+          <t>https://www.youtube.com/shorts/Sw3yl4ViZ7Q</t>
         </is>
       </c>
     </row>
     <row r="192" ht="22" customHeight="1">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>Why struggle when you can learn smarter?</t>
+          <t>Your phone into cctv</t>
         </is>
       </c>
       <c r="C192" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Why+struggle+when+you+can+learn+smarter</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Why struggle when you can learn smarter?</t>
+          <t>Online productivity web tool featured in TrickPilot: Turn your Phone Into CCTV</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>Why struggle when you can learn smarter?</t>
+          <t>Turn your Phone Into CCTV</t>
         </is>
       </c>
       <c r="F192" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/KLEFeEXkzu4</t>
+          <t>https://www.youtube.com/shorts/KpXYsI8lZ0Y</t>
         </is>
       </c>
     </row>
     <row r="193" ht="22" customHeight="1">
       <c r="A193" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>Windows Telemetry</t>
+          <t>Your website with joonweb</t>
         </is>
       </c>
       <c r="C193" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Windows+Telemetry</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D193" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Windows Telemetry</t>
+          <t>Online productivity web tool featured in TrickPilot: Build Your Website With JoonWeb</t>
         </is>
       </c>
       <c r="E193" s="4" t="inlineStr">
         <is>
-          <t>Windows Telemetry</t>
+          <t>Build Your Website With JoonWeb</t>
         </is>
       </c>
       <c r="F193" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/Bq0p3o3taZ0</t>
+          <t>https://www.youtube.com/shorts/w4e8No8Y8Js</t>
         </is>
       </c>
     </row>
     <row r="194" ht="22" customHeight="1">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>🎨 Design, 3D &amp; Graphics</t>
         </is>
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>Wish Birthday like this</t>
+          <t>How to create passport size photo</t>
         </is>
       </c>
       <c r="C194" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Wish+Birthday+like+this</t>
+          <t>https://toools.design</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Wish Birthday like this</t>
+          <t>Creative design web tool featured in TrickPilot: How to Create Passport Size Photo</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>Wish Birthday like this</t>
+          <t>How to Create Passport Size Photo</t>
         </is>
       </c>
       <c r="F194" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/VQ6pgCCoNcQ</t>
+          <t>https://www.youtube.com/shorts/mjzc-LwJY-U</t>
         </is>
       </c>
     </row>
     <row r="195" ht="22" customHeight="1">
       <c r="A195" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>🎨 Design, 3D &amp; Graphics</t>
         </is>
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>World tour with 0 money</t>
+          <t>How to edit photo in one click</t>
         </is>
       </c>
       <c r="C195" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=World+tour+with+0+money</t>
+          <t>https://toools.design</t>
         </is>
       </c>
       <c r="D195" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: World tour with 0 money</t>
+          <t>Creative design web tool featured in TrickPilot: How to edit photo in one click</t>
         </is>
       </c>
       <c r="E195" s="4" t="inlineStr">
         <is>
-          <t>World tour with 0 money</t>
+          <t>How to edit photo in one click</t>
         </is>
       </c>
       <c r="F195" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/uXrgTC1cEws</t>
+          <t>https://www.youtube.com/shorts/dSf2xBDgmrE</t>
         </is>
       </c>
     </row>
     <row r="196" ht="22" customHeight="1">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>🎨 Design, 3D &amp; Graphics</t>
         </is>
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>You Dont Need Antivirus</t>
+          <t>Passport size photo in just 2 min</t>
         </is>
       </c>
       <c r="C196" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=You+Dont+Need+Antivirus</t>
+          <t>https://toools.design</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: You Dont Need Antivirus</t>
+          <t>Creative design web tool featured in TrickPilot: Create Passport Size Photo In Just 2 Min</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>You Dont Need Antivirus</t>
+          <t>Create Passport Size Photo In Just 2 Min</t>
         </is>
       </c>
       <c r="F196" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/g-bRucHk7OE</t>
+          <t>https://www.youtube.com/shorts/FZVwlYHPlQo</t>
         </is>
       </c>
     </row>
     <row r="197" ht="22" customHeight="1">
       <c r="A197" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>🎨 Design, 3D &amp; Graphics</t>
         </is>
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>Your Pc is always in hibernation</t>
+          <t>Passport size photos</t>
         </is>
       </c>
       <c r="C197" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Your+Pc+is+always+in+hibernation</t>
+          <t>https://toools.design</t>
         </is>
       </c>
       <c r="D197" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Your Pc is always in hibernation</t>
+          <t>Creative design web tool featured in TrickPilot: Create Passport Size photos</t>
         </is>
       </c>
       <c r="E197" s="4" t="inlineStr">
         <is>
-          <t>Your Pc is always in hibernation</t>
+          <t>Create Passport Size photos</t>
         </is>
       </c>
       <c r="F197" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/Sw3yl4ViZ7Q</t>
+          <t>https://www.youtube.com/shorts/l598tAICQoI</t>
         </is>
       </c>
     </row>
     <row r="198" ht="22" customHeight="1">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>🎵 Audio, Voice &amp; Music</t>
         </is>
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>business tips boost your business</t>
+          <t>Suno AI</t>
         </is>
       </c>
       <c r="C198" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=business+tips+boost+your+business</t>
+          <t>https://suno.com</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: business tips boost your business</t>
+          <t>Generate full songs with vocals, instruments, and custom lyrics using AI prompts.</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>business tips boost your business</t>
+          <t>Audio overview is my personal favourite</t>
         </is>
       </c>
       <c r="F198" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/Gp_jlrwz-HI</t>
+          <t>https://www.youtube.com/shorts/lXYJktKJ-Vc</t>
         </is>
       </c>
     </row>
     <row r="199" ht="22" customHeight="1">
       <c r="A199" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>💻 Coding &amp; Web Development</t>
         </is>
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>gmail tips</t>
+          <t>Cool app for student</t>
         </is>
       </c>
       <c r="C199" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=gmail+tips</t>
+          <t>https://replit.com</t>
         </is>
       </c>
       <c r="D199" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: gmail tips</t>
+          <t>Developer software platform featured in TrickPilot: Cool App for student</t>
         </is>
       </c>
       <c r="E199" s="4" t="inlineStr">
         <is>
-          <t>gmail tips</t>
+          <t>Cool App for student</t>
         </is>
       </c>
       <c r="F199" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/w8BfmtPCtLM</t>
+          <t>https://www.youtube.com/shorts/m8SCG3vrNyw</t>
         </is>
       </c>
     </row>
     <row r="200" ht="22" customHeight="1">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>💻 Coding &amp; Web Development</t>
         </is>
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>gmail tips create template</t>
+          <t>Different way to lock your chat</t>
         </is>
       </c>
       <c r="C200" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=gmail+tips+create+template</t>
+          <t>https://replit.com</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: gmail tips create template</t>
+          <t>Developer software platform featured in TrickPilot: Different Way To Lock Your Chat</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>gmail tips create template</t>
+          <t>Different Way To Lock Your Chat</t>
         </is>
       </c>
       <c r="F200" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/n_lEBYQU9PM</t>
+          <t>https://www.youtube.com/shorts/pMD1J1_3rlg</t>
         </is>
       </c>
     </row>
     <row r="201" ht="22" customHeight="1">
       <c r="A201" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>💻 Coding &amp; Web Development</t>
         </is>
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>gmail tips jo dimak hila de</t>
+          <t>DistroSea</t>
         </is>
       </c>
       <c r="C201" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=gmail+tips+jo+dimak+hila+de</t>
+          <t>https://distrosea.com</t>
         </is>
       </c>
       <c r="D201" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: gmail tips jo dimak hila de</t>
+          <t>Test drive and run Linux operating system distributions directly in your web browser.</t>
         </is>
       </c>
       <c r="E201" s="4" t="inlineStr">
         <is>
-          <t>gmail tips jo dimak hila de</t>
+          <t>Ever thought if switching to linux ? Try this.</t>
         </is>
       </c>
       <c r="F201" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/HPS-pE0ykho</t>
+          <t>https://www.youtube.com/shorts/qJXONJPgH8I</t>
         </is>
       </c>
     </row>
     <row r="202" ht="22" customHeight="1">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>💻 Coding &amp; Web Development</t>
         </is>
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>iPhones tips</t>
+          <t>MetaGPT</t>
         </is>
       </c>
       <c r="C202" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=iPhones+tips</t>
+          <t>https://github.com/geekan/MetaGPT</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: iPhones tips</t>
+          <t>Multi-agent framework where AI engineers, PMs, and architects build software autonomously.</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>iPhones tips</t>
+          <t>60 Ai Agents working on one project at the same time</t>
         </is>
       </c>
       <c r="F202" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/PBpEO6XmN68</t>
+          <t>https://www.youtube.com/shorts/KqpjMg8mBmc</t>
         </is>
       </c>
     </row>
     <row r="203" ht="22" customHeight="1">
       <c r="A203" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>💻 Coding &amp; Web Development</t>
         </is>
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>pc tips ab koi hack nai kar payga</t>
+          <t>Should be afraid of or be happy ?</t>
         </is>
       </c>
       <c r="C203" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=pc+tips+ab+koi+hack+nai+kar+payga</t>
+          <t>https://replit.com</t>
         </is>
       </c>
       <c r="D203" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: pc tips ab koi hack nai kar payga</t>
+          <t>Developer software platform featured in TrickPilot: Should be Afraid of or be Happy ?</t>
         </is>
       </c>
       <c r="E203" s="4" t="inlineStr">
         <is>
-          <t>pc tips ab koi hack nai kar payga</t>
+          <t>Should be Afraid of or be Happy ?</t>
         </is>
       </c>
       <c r="F203" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/Kif7ARVC38M</t>
+          <t>https://www.youtube.com/shorts/McHYFVZMwQ0</t>
         </is>
       </c>
     </row>
     <row r="204" ht="22" customHeight="1">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>💻 Coding &amp; Web Development</t>
         </is>
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>pc tips access your files anywhere</t>
+          <t>Use this cool application</t>
         </is>
       </c>
       <c r="C204" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=pc+tips+access+your+files+anywhere</t>
+          <t>https://replit.com</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: pc tips access your files anywhere</t>
+          <t>Developer software platform featured in TrickPilot: Use this cool Application</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>pc tips access your files anywhere</t>
+          <t>Use this cool Application</t>
         </is>
       </c>
       <c r="F204" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/uuVth_awCoc</t>
+          <t>https://www.youtube.com/shorts/F1e0009-XCk</t>
         </is>
       </c>
     </row>
     <row r="205" ht="22" customHeight="1">
       <c r="A205" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>💻 Coding &amp; Web Development</t>
         </is>
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>pc tips change your boring desktop</t>
+          <t>Web apps in seconds</t>
         </is>
       </c>
       <c r="C205" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=pc+tips+change+your+boring+desktop</t>
+          <t>https://replit.com</t>
         </is>
       </c>
       <c r="D205" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: pc tips change your boring desktop</t>
+          <t>Developer software platform featured in TrickPilot: Create web apps in seconds</t>
         </is>
       </c>
       <c r="E205" s="4" t="inlineStr">
         <is>
-          <t>pc tips change your boring desktop</t>
+          <t>Create web apps in seconds</t>
         </is>
       </c>
       <c r="F205" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/fIYtXAHDJ4M</t>
+          <t>https://www.youtube.com/shorts/SgEOtjHEWiA</t>
         </is>
       </c>
     </row>
     <row r="206" ht="22" customHeight="1">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>💻 Coding &amp; Web Development</t>
         </is>
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>pc tips mobile game khelo ab pc mein</t>
+          <t>Whatsapp new feature</t>
         </is>
       </c>
       <c r="C206" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=pc+tips+mobile+game+khelo+ab+pc+mein</t>
+          <t>https://replit.com</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: pc tips mobile game khelo ab pc mein</t>
+          <t>Developer software platform featured in TrickPilot: WhatsApp New Feature</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>pc tips mobile game khelo ab pc mein</t>
+          <t>WhatsApp New Feature</t>
         </is>
       </c>
       <c r="F206" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/Z67GqoZ59RA</t>
+          <t>https://www.youtube.com/shorts/tr686LQDlBQ</t>
         </is>
       </c>
     </row>
     <row r="207" ht="22" customHeight="1">
       <c r="A207" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>💻 Coding &amp; Web Development</t>
         </is>
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>pc tips open bios directly</t>
+          <t>Whatsapp tipslock your whatsapp in pc</t>
         </is>
       </c>
       <c r="C207" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=pc+tips+open+bios+directly</t>
+          <t>https://replit.com</t>
         </is>
       </c>
       <c r="D207" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: pc tips open bios directly</t>
+          <t>Developer software platform featured in TrickPilot: whatsApp tipslock your whatsApp in PC</t>
         </is>
       </c>
       <c r="E207" s="4" t="inlineStr">
         <is>
-          <t>pc tips open bios directly</t>
+          <t>whatsApp tipslock your whatsApp in PC</t>
         </is>
       </c>
       <c r="F207" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/Aa_TzaEdDKQ</t>
+          <t>https://www.youtube.com/shorts/iI_-K0Y9vJg</t>
         </is>
       </c>
     </row>
     <row r="208" ht="22" customHeight="1">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>💻 Coding &amp; Web Development</t>
         </is>
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>pc tips sabhi problams ka solution</t>
+          <t>v0 by Vercel</t>
         </is>
       </c>
       <c r="C208" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=pc+tips+sabhi+problams+ka+solution</t>
+          <t>https://v0.dev</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: pc tips sabhi problams ka solution</t>
+          <t>Generative UI system by Vercel that converts natural language prompts into React code.</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>pc tips sabhi problams ka solution</t>
+          <t>Turn Idea into apps - Instantly</t>
         </is>
       </c>
       <c r="F208" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/cb2SgUgUbww</t>
+          <t>https://www.youtube.com/shorts/b86HZqtXRVo</t>
         </is>
       </c>
     </row>
     <row r="209" ht="22" customHeight="1">
       <c r="A209" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>📚 Learning, Study &amp; Research</t>
         </is>
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>pc tipsand hack</t>
+          <t>1000s of live wallpapers for free</t>
         </is>
       </c>
       <c r="C209" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=pc+tipsand+hack</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D209" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: pc tipsand hack</t>
+          <t>Educational study resource featured in TrickPilot: Get 1000s of Live Wallpapers for free</t>
         </is>
       </c>
       <c r="E209" s="4" t="inlineStr">
         <is>
-          <t>pc tipsand hack</t>
+          <t>Get 1000s of Live Wallpapers for free</t>
         </is>
       </c>
       <c r="F209" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/1RzEFV4bzuw</t>
+          <t>https://www.youtube.com/shorts/9r0RVEhOPzI</t>
         </is>
       </c>
     </row>
     <row r="210" ht="22" customHeight="1">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>📚 Learning, Study &amp; Research</t>
         </is>
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>pc tipsand hack Gmail Tips Protect your email</t>
+          <t>3 most useful websites for students</t>
         </is>
       </c>
       <c r="C210" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=pc+tipsand+hack+Gmail+Tips+Protect+your+email</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: pc tipsand hack Gmail Tips Protect your email</t>
+          <t>Educational study resource featured in TrickPilot: 3 Most Useful Websites For Students</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>pc tipsand hack Gmail Tips Protect your email</t>
+          <t>3 Most Useful Websites For Students</t>
         </is>
       </c>
       <c r="F210" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/UAY-uHYXMeU</t>
+          <t>https://www.youtube.com/shorts/t_CIeNfo4JI</t>
         </is>
       </c>
     </row>
     <row r="211" ht="22" customHeight="1">
       <c r="A211" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>📚 Learning, Study &amp; Research</t>
         </is>
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>powerful extension</t>
+          <t>Google search trick for students</t>
         </is>
       </c>
       <c r="C211" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=powerful+extension</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D211" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: powerful extension</t>
+          <t>Educational study resource featured in TrickPilot: Google search trick for Students</t>
         </is>
       </c>
       <c r="E211" s="4" t="inlineStr">
         <is>
-          <t>powerful extension</t>
+          <t>Google search trick for Students</t>
         </is>
       </c>
       <c r="F211" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/oV034iwOpgA</t>
+          <t>https://www.youtube.com/shorts/C2Ardr1bZ40</t>
         </is>
       </c>
     </row>
     <row r="212" ht="22" customHeight="1">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>📚 Learning, Study &amp; Research</t>
         </is>
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>powerful website</t>
+          <t>Students save this video</t>
         </is>
       </c>
       <c r="C212" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=powerful+website</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: powerful website</t>
+          <t>Educational study resource featured in TrickPilot: Students Save this video</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>powerful website</t>
+          <t>Students Save this video</t>
         </is>
       </c>
       <c r="F212" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/4tjNhjE3iSk</t>
+          <t>https://www.youtube.com/shorts/27vZ-IjaCZQ</t>
         </is>
       </c>
     </row>
     <row r="213" ht="22" customHeight="1">
       <c r="A213" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>📚 Learning, Study &amp; Research</t>
         </is>
       </c>
       <c r="B213" s="4" t="inlineStr">
         <is>
-          <t>scam alerts bank account khali hone se bacho</t>
+          <t>Students tips</t>
         </is>
       </c>
       <c r="C213" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=scam+alerts+bank+account+khali+hone+se+bacho</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D213" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: scam alerts bank account khali hone se bacho</t>
+          <t>Educational study resource featured in TrickPilot: students tips</t>
         </is>
       </c>
       <c r="E213" s="4" t="inlineStr">
         <is>
-          <t>scam alerts bank account khali hone se bacho</t>
+          <t>students tips</t>
         </is>
       </c>
       <c r="F213" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/roqvFv5XiqA</t>
+          <t>https://www.youtube.com/shorts/I8FB50ecfpQ</t>
         </is>
       </c>
     </row>
     <row r="214" ht="22" customHeight="1">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>🤖 AI &amp; Machine Learning Tools</t>
         </is>
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>secret website</t>
+          <t>Anything by professionals</t>
         </is>
       </c>
       <c r="C214" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=secret+website</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: secret website</t>
+          <t>AI application featured in TrickPilot: Learn Anything by professionals</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>secret website</t>
+          <t>Learn Anything by professionals</t>
         </is>
       </c>
       <c r="F214" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/C9dIEFY7h7M</t>
+          <t>https://www.youtube.com/shorts/K4OxlX6n1NY</t>
         </is>
       </c>
     </row>
     <row r="215" ht="22" customHeight="1">
       <c r="A215" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>🤖 AI &amp; Machine Learning Tools</t>
         </is>
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>students tips</t>
+          <t>Best tools of 2025</t>
         </is>
       </c>
       <c r="C215" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=students+tips</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D215" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: students tips</t>
+          <t>AI application featured in TrickPilot: Best tools of 2025</t>
         </is>
       </c>
       <c r="E215" s="4" t="inlineStr">
         <is>
-          <t>students tips</t>
+          <t>Best tools of 2025</t>
         </is>
       </c>
       <c r="F215" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/I8FB50ecfpQ</t>
+          <t>https://www.youtube.com/shorts/IFSd72PuERo</t>
         </is>
       </c>
     </row>
     <row r="216" ht="22" customHeight="1">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>🤖 AI &amp; Machine Learning Tools</t>
         </is>
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>whatsApp tipslock your whatsApp in PC</t>
+          <t>Chat gpt always agrees with you</t>
         </is>
       </c>
       <c r="C216" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=whatsApp+tipslock+your+whatsApp+in+PC</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: whatsApp tipslock your whatsApp in PC</t>
+          <t>AI application featured in TrickPilot: Chat GPT always agrees with you</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>whatsApp tipslock your whatsApp in PC</t>
+          <t>Chat GPT always agrees with you</t>
         </is>
       </c>
       <c r="F216" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/iI_-K0Y9vJg</t>
+          <t>https://www.youtube.com/shorts/9UX2pBmHj1k</t>
         </is>
       </c>
     </row>
@@ -7401,27 +7401,27 @@
       </c>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t>Best AI tools that makes life Easy</t>
+          <t>Chat gpt getting crazier</t>
         </is>
       </c>
       <c r="C217" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Best+AI+tools+that+makes+life+Easy</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D217" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Best AI tools that makes life Easy</t>
+          <t>AI application featured in TrickPilot: Chat Gpt getting Crazier</t>
         </is>
       </c>
       <c r="E217" s="4" t="inlineStr">
         <is>
-          <t>Best AI tools that makes life Easy</t>
+          <t>Chat Gpt getting Crazier</t>
         </is>
       </c>
       <c r="F217" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/Rw9IFUfrvZg</t>
+          <t>https://www.youtube.com/shorts/hd8UxJKGPJ8</t>
         </is>
       </c>
     </row>
@@ -7433,27 +7433,27 @@
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>Best tools of 2025</t>
+          <t>Chat gpt is astrologer</t>
         </is>
       </c>
       <c r="C218" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Best+tools+of+2025</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Best tools of 2025</t>
+          <t>AI application featured in TrickPilot: Chat Gpt Is Astrologer</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>Best tools of 2025</t>
+          <t>Chat Gpt Is Astrologer</t>
         </is>
       </c>
       <c r="F218" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/IFSd72PuERo</t>
+          <t>https://www.youtube.com/shorts/rQBVZu7KBVU</t>
         </is>
       </c>
     </row>
@@ -7465,17 +7465,17 @@
       </c>
       <c r="B219" s="4" t="inlineStr">
         <is>
-          <t>Chat GPT Trick</t>
+          <t>Chat gpt trick</t>
         </is>
       </c>
       <c r="C219" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Chat+GPT+Trick</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D219" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Chat GPT Trick</t>
+          <t>AI application featured in TrickPilot: Chat GPT Trick</t>
         </is>
       </c>
       <c r="E219" s="4" t="inlineStr">
@@ -7497,27 +7497,27 @@
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>Chat GPT always agrees with you</t>
+          <t>Chat-gpt will sound like human</t>
         </is>
       </c>
       <c r="C220" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Chat+GPT+always+agrees+with+you</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Chat GPT always agrees with you</t>
+          <t>AI application featured in TrickPilot: Chat-GPT will sound like human</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>Chat GPT always agrees with you</t>
+          <t>Chat-GPT will sound like human</t>
         </is>
       </c>
       <c r="F220" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/9UX2pBmHj1k</t>
+          <t>https://www.youtube.com/shorts/ihT8kjKUREA</t>
         </is>
       </c>
     </row>
@@ -7529,27 +7529,27 @@
       </c>
       <c r="B221" s="4" t="inlineStr">
         <is>
-          <t>Chat Gpt Is Astrologer</t>
+          <t>Comment for prompt</t>
         </is>
       </c>
       <c r="C221" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Chat+Gpt+Is+Astrologer</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D221" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Chat Gpt Is Astrologer</t>
+          <t>AI application featured in TrickPilot: Check Comment for Prompt</t>
         </is>
       </c>
       <c r="E221" s="4" t="inlineStr">
         <is>
-          <t>Chat Gpt Is Astrologer</t>
+          <t>Check Comment for Prompt</t>
         </is>
       </c>
       <c r="F221" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/rQBVZu7KBVU</t>
+          <t>https://www.youtube.com/shorts/C5q2TZVHCyI</t>
         </is>
       </c>
     </row>
@@ -7561,27 +7561,27 @@
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>Chat Gpt getting Crazier</t>
+          <t>Humanize ai written content</t>
         </is>
       </c>
       <c r="C222" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Chat+Gpt+getting+Crazier</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Chat Gpt getting Crazier</t>
+          <t>AI application featured in TrickPilot: Humanize AI Written Content</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>Chat Gpt getting Crazier</t>
+          <t>Humanize AI Written Content</t>
         </is>
       </c>
       <c r="F222" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/hd8UxJKGPJ8</t>
+          <t>https://www.youtube.com/shorts/-eKpiEBJnC8</t>
         </is>
       </c>
     </row>
@@ -7593,27 +7593,27 @@
       </c>
       <c r="B223" s="4" t="inlineStr">
         <is>
-          <t>Chat-GPT will sound like human</t>
+          <t>I made a complete song with ai</t>
         </is>
       </c>
       <c r="C223" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=ChatGPT+will+sound+like+human</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D223" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Chat-GPT will sound like human</t>
+          <t>AI application featured in TrickPilot: I made a complete song with AI</t>
         </is>
       </c>
       <c r="E223" s="4" t="inlineStr">
         <is>
-          <t>Chat-GPT will sound like human</t>
+          <t>I made a complete song with AI</t>
         </is>
       </c>
       <c r="F223" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/ihT8kjKUREA</t>
+          <t>https://www.youtube.com/shorts/Bub71RK3Fgk</t>
         </is>
       </c>
     </row>
@@ -7625,27 +7625,27 @@
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>Humanize AI Written Content</t>
+          <t>Multiple ai models at one place</t>
         </is>
       </c>
       <c r="C224" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Humanize+AI+Written+Content</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Humanize AI Written Content</t>
+          <t>AI application featured in TrickPilot: Multiple AI models at one place</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>Humanize AI Written Content</t>
+          <t>Multiple AI models at one place</t>
         </is>
       </c>
       <c r="F224" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/-eKpiEBJnC8</t>
+          <t>https://www.youtube.com/shorts/y0dxSwUwhxo</t>
         </is>
       </c>
     </row>
@@ -7657,27 +7657,27 @@
       </c>
       <c r="B225" s="4" t="inlineStr">
         <is>
-          <t>I made a complete song with AI</t>
+          <t>No relatives, only robots</t>
         </is>
       </c>
       <c r="C225" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=I+made+a+complete+song+with+AI</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D225" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: I made a complete song with AI</t>
+          <t>AI application featured in TrickPilot: No relatives, only robots</t>
         </is>
       </c>
       <c r="E225" s="4" t="inlineStr">
         <is>
-          <t>I made a complete song with AI</t>
+          <t>No relatives, only robots</t>
         </is>
       </c>
       <c r="F225" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/Bub71RK3Fgk</t>
+          <t>https://www.youtube.com/shorts/WURbOfN2aOE</t>
         </is>
       </c>
     </row>
@@ -7689,27 +7689,27 @@
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>Learn Anything by professionals</t>
+          <t>This tool bypass all detection tools</t>
         </is>
       </c>
       <c r="C226" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Learn+Anything+by+professionals</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Learn Anything by professionals</t>
+          <t>AI application featured in TrickPilot: This Tool Bypass All Detection Tools</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>Learn Anything by professionals</t>
+          <t>This Tool Bypass All Detection Tools</t>
         </is>
       </c>
       <c r="F226" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/K4OxlX6n1NY</t>
+          <t>https://www.youtube.com/shorts/Mypf-QlKzjw</t>
         </is>
       </c>
     </row>
@@ -7721,27 +7721,27 @@
       </c>
       <c r="B227" s="4" t="inlineStr">
         <is>
-          <t>Multiple AI models at one place</t>
+          <t>This tool will bypass ai detection tools</t>
         </is>
       </c>
       <c r="C227" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Multiple+AI+models+at+one+place</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D227" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Multiple AI models at one place</t>
+          <t>AI application featured in TrickPilot: This Tool Will Bypass Ai Detection Tools</t>
         </is>
       </c>
       <c r="E227" s="4" t="inlineStr">
         <is>
-          <t>Multiple AI models at one place</t>
+          <t>This Tool Will Bypass Ai Detection Tools</t>
         </is>
       </c>
       <c r="F227" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/y0dxSwUwhxo</t>
+          <t>https://www.youtube.com/shorts/gvT29dkQhzw</t>
         </is>
       </c>
     </row>
@@ -7753,27 +7753,27 @@
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>This Tool Bypass All Detection Tools</t>
+          <t>Toolify.ai</t>
         </is>
       </c>
       <c r="C228" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=This+Tool+Bypass+All+Detection+Tools</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: This Tool Bypass All Detection Tools</t>
+          <t>The world's most comprehensive directory of new AI tools, apps, and software updated daily.</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>This Tool Bypass All Detection Tools</t>
+          <t>Best AI tools that makes life Easy</t>
         </is>
       </c>
       <c r="F228" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/Mypf-QlKzjw</t>
+          <t>https://www.youtube.com/shorts/Rw9IFUfrvZg</t>
         </is>
       </c>
     </row>
@@ -7785,27 +7785,27 @@
       </c>
       <c r="B229" s="4" t="inlineStr">
         <is>
-          <t>This Tool Will Bypass Ai Detection Tools</t>
+          <t>Try these two prompts in chat gpt [</t>
         </is>
       </c>
       <c r="C229" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=This+Tool+Will+Bypass+Ai+Detection+Tools</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D229" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: This Tool Will Bypass Ai Detection Tools</t>
+          <t>AI application featured in TrickPilot: Try these two prompts in Chat Gpt [ Not for Kids ]</t>
         </is>
       </c>
       <c r="E229" s="4" t="inlineStr">
         <is>
-          <t>This Tool Will Bypass Ai Detection Tools</t>
+          <t>Try these two prompts in Chat Gpt [ Not for Kids ]</t>
         </is>
       </c>
       <c r="F229" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/gvT29dkQhzw</t>
+          <t>https://www.youtube.com/shorts/DScbrafsckQ</t>
         </is>
       </c>
     </row>
@@ -7817,57 +7817,25 @@
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>Try these two prompts in Chat Gpt [ Not for K</t>
+          <t>Use chinas new ai chatbot</t>
         </is>
       </c>
       <c r="C230" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Try+these+two+prompts+in+Chat+Gpt++Not+for+Kids</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in TrickPilot showcase: Try these two prompts in Chat Gpt [ Not for Kids ]</t>
+          <t>AI application featured in TrickPilot: Use Chinas new AI Chatbot</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>Try these two prompts in Chat Gpt [ Not for Kids ]</t>
+          <t>Use Chinas new AI Chatbot</t>
         </is>
       </c>
       <c r="F230" s="3" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/shorts/DScbrafsckQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="231" ht="22" customHeight="1">
-      <c r="A231" s="4" t="inlineStr">
-        <is>
-          <t>🤖 AI &amp; Machine Learning Tools</t>
-        </is>
-      </c>
-      <c r="B231" s="4" t="inlineStr">
-        <is>
-          <t>Use Chinas new AI Chatbot</t>
-        </is>
-      </c>
-      <c r="C231" s="5" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=Use+Chinas+new+AI+Chatbot</t>
-        </is>
-      </c>
-      <c r="D231" s="4" t="inlineStr">
-        <is>
-          <t>Featured web tool in TrickPilot showcase: Use Chinas new AI Chatbot</t>
-        </is>
-      </c>
-      <c r="E231" s="4" t="inlineStr">
-        <is>
-          <t>Use Chinas new AI Chatbot</t>
-        </is>
-      </c>
-      <c r="F231" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/shorts/G18Fav7Q2Fk</t>
         </is>
@@ -8333,8 +8301,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F229" r:id="rId456"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C230" r:id="rId457"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F230" r:id="rId458"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C231" r:id="rId459"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F231" r:id="rId460"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
